--- a/available-bots.xlsx
+++ b/available-bots.xlsx
@@ -489,9 +489,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>16.9.7708676+branch.releases-16-9.code.publictencent.content.release</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>16.13.7915903+branch.releases-16-13.code.publictencent.content.release</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1151,11 +1151,7 @@
           <t>2024-09-30 07-29-57</t>
         </is>
       </c>
-      <c r="X4" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X4" s="0" t="inlineStr"/>
       <c r="Y4" s="0" t="inlineStr"/>
       <c r="Z4" s="0" t="inlineStr"/>
       <c r="AA4" s="0" t="inlineStr"/>
@@ -1419,13 +1415,21 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N6" s="0" t="inlineStr"/>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="O6" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="P6" s="0" t="inlineStr"/>
+      <c r="P6" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q6" s="0" t="inlineStr"/>
       <c r="R6" s="0" t="inlineStr"/>
       <c r="S6" s="0" t="inlineStr">
@@ -1449,17 +1453,9 @@
           <t>2024-11-21 23-33-50</t>
         </is>
       </c>
-      <c r="X6" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X6" s="0" t="inlineStr"/>
       <c r="Y6" s="0" t="inlineStr"/>
-      <c r="Z6" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z6" s="0" t="inlineStr"/>
       <c r="AA6" s="0" t="inlineStr"/>
       <c r="AB6" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1602,11 @@
       </c>
       <c r="X7" s="0" t="inlineStr"/>
       <c r="Y7" s="0" t="inlineStr"/>
-      <c r="Z7" s="0" t="inlineStr"/>
+      <c r="Z7" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA7" s="0" t="inlineStr"/>
       <c r="AB7" s="0" t="inlineStr">
         <is>
@@ -1900,11 +1900,7 @@
       </c>
       <c r="X9" s="0" t="inlineStr"/>
       <c r="Y9" s="0" t="inlineStr"/>
-      <c r="Z9" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z9" s="0" t="inlineStr"/>
       <c r="AA9" s="0" t="inlineStr"/>
       <c r="AB9" s="0" t="inlineStr">
         <is>
@@ -3539,11 +3535,7 @@
           <t>2024-11-21 23-02-29</t>
         </is>
       </c>
-      <c r="X20" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X20" s="0" t="inlineStr"/>
       <c r="Y20" s="0" t="inlineStr"/>
       <c r="Z20" s="0" t="inlineStr">
         <is>
@@ -3847,11 +3839,7 @@
       </c>
       <c r="X22" s="0" t="inlineStr"/>
       <c r="Y22" s="0" t="inlineStr"/>
-      <c r="Z22" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z22" s="0" t="inlineStr"/>
       <c r="AA22" s="0" t="inlineStr"/>
       <c r="AB22" s="0" t="inlineStr">
         <is>
@@ -3998,7 +3986,11 @@
       </c>
       <c r="X23" s="0" t="inlineStr"/>
       <c r="Y23" s="0" t="inlineStr"/>
-      <c r="Z23" s="0" t="inlineStr"/>
+      <c r="Z23" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA23" s="0" t="inlineStr"/>
       <c r="AB23" s="0" t="inlineStr">
         <is>
@@ -5196,11 +5188,7 @@
           <t>2024-07-06 23-55-14</t>
         </is>
       </c>
-      <c r="X31" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X31" s="0" t="inlineStr"/>
       <c r="Y31" s="0" t="inlineStr"/>
       <c r="Z31" s="0" t="inlineStr"/>
       <c r="AA31" s="0" t="inlineStr"/>
@@ -5471,11 +5459,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="Q33" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Q33" s="0" t="inlineStr"/>
       <c r="R33" s="0" t="inlineStr"/>
       <c r="S33" s="0" t="inlineStr">
         <is>
@@ -5804,13 +5788,13 @@
           <t>2020-01-27 22-43-05</t>
         </is>
       </c>
-      <c r="X35" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X35" s="0" t="inlineStr"/>
       <c r="Y35" s="0" t="inlineStr"/>
-      <c r="Z35" s="0" t="inlineStr"/>
+      <c r="Z35" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA35" s="0" t="inlineStr"/>
       <c r="AB35" s="0" t="inlineStr">
         <is>
@@ -5957,11 +5941,7 @@
       </c>
       <c r="X36" s="0" t="inlineStr"/>
       <c r="Y36" s="0" t="inlineStr"/>
-      <c r="Z36" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z36" s="0" t="inlineStr"/>
       <c r="AA36" s="0" t="inlineStr"/>
       <c r="AB36" s="0" t="inlineStr">
         <is>
@@ -6694,11 +6674,7 @@
           <t>2020-02-01 12-55-49</t>
         </is>
       </c>
-      <c r="X41" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X41" s="0" t="inlineStr"/>
       <c r="Y41" s="0" t="inlineStr"/>
       <c r="Z41" s="0" t="inlineStr">
         <is>
@@ -7000,11 +6976,7 @@
           <t>2021-12-23 20-26-31</t>
         </is>
       </c>
-      <c r="X43" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X43" s="0" t="inlineStr"/>
       <c r="Y43" s="0" t="inlineStr"/>
       <c r="Z43" s="0" t="inlineStr"/>
       <c r="AA43" s="0" t="inlineStr"/>
@@ -7269,11 +7241,7 @@
       <c r="L45" s="0" t="inlineStr"/>
       <c r="M45" s="0" t="inlineStr"/>
       <c r="N45" s="0" t="inlineStr"/>
-      <c r="O45" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="O45" s="0" t="inlineStr"/>
       <c r="P45" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -7304,7 +7272,11 @@
       </c>
       <c r="X45" s="0" t="inlineStr"/>
       <c r="Y45" s="0" t="inlineStr"/>
-      <c r="Z45" s="0" t="inlineStr"/>
+      <c r="Z45" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA45" s="0" t="inlineStr"/>
       <c r="AB45" s="0" t="inlineStr">
         <is>
@@ -7896,7 +7868,11 @@
       </c>
       <c r="X49" s="0" t="inlineStr"/>
       <c r="Y49" s="0" t="inlineStr"/>
-      <c r="Z49" s="0" t="inlineStr"/>
+      <c r="Z49" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA49" s="0" t="inlineStr"/>
       <c r="AB49" s="0" t="inlineStr">
         <is>
@@ -8007,11 +7983,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N50" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N50" s="0" t="inlineStr"/>
       <c r="O50" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -8043,11 +8015,7 @@
       </c>
       <c r="X50" s="0" t="inlineStr"/>
       <c r="Y50" s="0" t="inlineStr"/>
-      <c r="Z50" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z50" s="0" t="inlineStr"/>
       <c r="AA50" s="0" t="inlineStr"/>
       <c r="AB50" s="0" t="inlineStr">
         <is>
@@ -9076,11 +9044,7 @@
       </c>
       <c r="X57" s="0" t="inlineStr"/>
       <c r="Y57" s="0" t="inlineStr"/>
-      <c r="Z57" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z57" s="0" t="inlineStr"/>
       <c r="AA57" s="0" t="inlineStr"/>
       <c r="AB57" s="0" t="inlineStr">
         <is>
@@ -9378,7 +9342,11 @@
       </c>
       <c r="X59" s="0" t="inlineStr"/>
       <c r="Y59" s="0" t="inlineStr"/>
-      <c r="Z59" s="0" t="inlineStr"/>
+      <c r="Z59" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA59" s="0" t="inlineStr"/>
       <c r="AB59" s="0" t="inlineStr">
         <is>
@@ -9817,11 +9785,7 @@
           <t>2022-11-05 15-12-11</t>
         </is>
       </c>
-      <c r="X62" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X62" s="0" t="inlineStr"/>
       <c r="Y62" s="0" t="inlineStr"/>
       <c r="Z62" s="0" t="inlineStr"/>
       <c r="AA62" s="0" t="inlineStr"/>
@@ -11079,9 +11043,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>16.9.7708676+branch.releases-16-9.code.publictencent.content.release</t>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>16.13.7915903+branch.releases-16-13.code.publictencent.content.release</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -11741,11 +11705,7 @@
           <t>2024-09-30 07-29-57</t>
         </is>
       </c>
-      <c r="X4" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X4" s="0" t="inlineStr"/>
       <c r="Y4" s="0" t="inlineStr"/>
       <c r="Z4" s="0" t="inlineStr"/>
       <c r="AA4" s="0" t="inlineStr"/>
@@ -12009,13 +11969,21 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N6" s="0" t="inlineStr"/>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="O6" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="P6" s="0" t="inlineStr"/>
+      <c r="P6" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q6" s="0" t="inlineStr"/>
       <c r="R6" s="0" t="inlineStr"/>
       <c r="S6" s="0" t="inlineStr">
@@ -12039,17 +12007,9 @@
           <t>2024-11-21 23-33-50</t>
         </is>
       </c>
-      <c r="X6" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X6" s="0" t="inlineStr"/>
       <c r="Y6" s="0" t="inlineStr"/>
-      <c r="Z6" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z6" s="0" t="inlineStr"/>
       <c r="AA6" s="0" t="inlineStr"/>
       <c r="AB6" s="0" t="inlineStr">
         <is>
@@ -12196,7 +12156,11 @@
       </c>
       <c r="X7" s="0" t="inlineStr"/>
       <c r="Y7" s="0" t="inlineStr"/>
-      <c r="Z7" s="0" t="inlineStr"/>
+      <c r="Z7" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA7" s="0" t="inlineStr"/>
       <c r="AB7" s="0" t="inlineStr">
         <is>
@@ -12274,7 +12238,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>费德提克</t>
+          <t>远古恐惧</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -12492,11 +12456,7 @@
           <t>2023-08-04 00-53-36</t>
         </is>
       </c>
-      <c r="X9" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X9" s="0" t="inlineStr"/>
       <c r="Y9" s="0" t="inlineStr"/>
       <c r="Z9" s="0" t="inlineStr"/>
       <c r="AA9" s="0" t="inlineStr"/>
@@ -12792,11 +12752,7 @@
       </c>
       <c r="X11" s="0" t="inlineStr"/>
       <c r="Y11" s="0" t="inlineStr"/>
-      <c r="Z11" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z11" s="0" t="inlineStr"/>
       <c r="AA11" s="0" t="inlineStr"/>
       <c r="AB11" s="0" t="inlineStr">
         <is>
@@ -14248,11 +14204,7 @@
       <c r="M21" s="0" t="inlineStr"/>
       <c r="N21" s="0" t="inlineStr"/>
       <c r="O21" s="0" t="inlineStr"/>
-      <c r="P21" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P21" s="0" t="inlineStr"/>
       <c r="Q21" s="0" t="inlineStr"/>
       <c r="R21" s="0" t="inlineStr">
         <is>
@@ -14280,11 +14232,7 @@
           <t>2023-10-03 15-43-15</t>
         </is>
       </c>
-      <c r="X21" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X21" s="0" t="inlineStr"/>
       <c r="Y21" s="0" t="inlineStr"/>
       <c r="Z21" s="0" t="inlineStr"/>
       <c r="AA21" s="0" t="inlineStr"/>
@@ -15321,11 +15269,7 @@
           <t>2024-11-21 23-02-29</t>
         </is>
       </c>
-      <c r="X28" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X28" s="0" t="inlineStr"/>
       <c r="Y28" s="0" t="inlineStr"/>
       <c r="Z28" s="0" t="inlineStr">
         <is>
@@ -15629,11 +15573,7 @@
       </c>
       <c r="X30" s="0" t="inlineStr"/>
       <c r="Y30" s="0" t="inlineStr"/>
-      <c r="Z30" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z30" s="0" t="inlineStr"/>
       <c r="AA30" s="0" t="inlineStr"/>
       <c r="AB30" s="0" t="inlineStr">
         <is>
@@ -16066,7 +16006,11 @@
       </c>
       <c r="X33" s="0" t="inlineStr"/>
       <c r="Y33" s="0" t="inlineStr"/>
-      <c r="Z33" s="0" t="inlineStr"/>
+      <c r="Z33" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA33" s="0" t="inlineStr"/>
       <c r="AB33" s="0" t="inlineStr">
         <is>
@@ -16213,7 +16157,11 @@
       </c>
       <c r="X34" s="0" t="inlineStr"/>
       <c r="Y34" s="0" t="inlineStr"/>
-      <c r="Z34" s="0" t="inlineStr"/>
+      <c r="Z34" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA34" s="0" t="inlineStr"/>
       <c r="AB34" s="0" t="inlineStr">
         <is>
@@ -16511,11 +16459,7 @@
       </c>
       <c r="X36" s="0" t="inlineStr"/>
       <c r="Y36" s="0" t="inlineStr"/>
-      <c r="Z36" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z36" s="0" t="inlineStr"/>
       <c r="AA36" s="0" t="inlineStr"/>
       <c r="AB36" s="0" t="inlineStr">
         <is>
@@ -17535,7 +17479,11 @@
           <t>√</t>
         </is>
       </c>
-      <c r="Q43" s="0" t="inlineStr"/>
+      <c r="Q43" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="R43" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -17564,7 +17512,11 @@
       </c>
       <c r="X43" s="0" t="inlineStr"/>
       <c r="Y43" s="0" t="inlineStr"/>
-      <c r="Z43" s="0" t="inlineStr"/>
+      <c r="Z43" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA43" s="0" t="inlineStr"/>
       <c r="AB43" s="0" t="inlineStr">
         <is>
@@ -17856,11 +17808,7 @@
           <t>2024-07-06 23-55-14</t>
         </is>
       </c>
-      <c r="X45" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X45" s="0" t="inlineStr"/>
       <c r="Y45" s="0" t="inlineStr"/>
       <c r="Z45" s="0" t="inlineStr"/>
       <c r="AA45" s="0" t="inlineStr"/>
@@ -18131,11 +18079,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="Q47" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Q47" s="0" t="inlineStr"/>
       <c r="R47" s="0" t="inlineStr"/>
       <c r="S47" s="0" t="inlineStr">
         <is>
@@ -18283,11 +18227,7 @@
         </is>
       </c>
       <c r="Q48" s="0" t="inlineStr"/>
-      <c r="R48" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="R48" s="0" t="inlineStr"/>
       <c r="S48" s="0" t="inlineStr">
         <is>
           <t>魔法伤害</t>
@@ -18762,13 +18702,13 @@
           <t>2020-01-27 22-43-05</t>
         </is>
       </c>
-      <c r="X51" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X51" s="0" t="inlineStr"/>
       <c r="Y51" s="0" t="inlineStr"/>
-      <c r="Z51" s="0" t="inlineStr"/>
+      <c r="Z51" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA51" s="0" t="inlineStr"/>
       <c r="AB51" s="0" t="inlineStr">
         <is>
@@ -19221,11 +19161,7 @@
       </c>
       <c r="X54" s="0" t="inlineStr"/>
       <c r="Y54" s="0" t="inlineStr"/>
-      <c r="Z54" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z54" s="0" t="inlineStr"/>
       <c r="AA54" s="0" t="inlineStr"/>
       <c r="AB54" s="0" t="inlineStr">
         <is>
@@ -19958,11 +19894,7 @@
           <t>2020-02-01 12-55-49</t>
         </is>
       </c>
-      <c r="X59" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X59" s="0" t="inlineStr"/>
       <c r="Y59" s="0" t="inlineStr"/>
       <c r="Z59" s="0" t="inlineStr">
         <is>
@@ -20701,11 +20633,7 @@
           <t>2021-12-23 20-26-31</t>
         </is>
       </c>
-      <c r="X64" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X64" s="0" t="inlineStr"/>
       <c r="Y64" s="0" t="inlineStr"/>
       <c r="Z64" s="0" t="inlineStr"/>
       <c r="AA64" s="0" t="inlineStr"/>
@@ -21117,11 +21045,7 @@
       <c r="L67" s="0" t="inlineStr"/>
       <c r="M67" s="0" t="inlineStr"/>
       <c r="N67" s="0" t="inlineStr"/>
-      <c r="O67" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="O67" s="0" t="inlineStr"/>
       <c r="P67" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -21152,7 +21076,11 @@
       </c>
       <c r="X67" s="0" t="inlineStr"/>
       <c r="Y67" s="0" t="inlineStr"/>
-      <c r="Z67" s="0" t="inlineStr"/>
+      <c r="Z67" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA67" s="0" t="inlineStr"/>
       <c r="AB67" s="0" t="inlineStr">
         <is>
@@ -21744,7 +21672,11 @@
       </c>
       <c r="X71" s="0" t="inlineStr"/>
       <c r="Y71" s="0" t="inlineStr"/>
-      <c r="Z71" s="0" t="inlineStr"/>
+      <c r="Z71" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA71" s="0" t="inlineStr"/>
       <c r="AB71" s="0" t="inlineStr">
         <is>
@@ -21855,11 +21787,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N72" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N72" s="0" t="inlineStr"/>
       <c r="O72" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -21891,11 +21819,7 @@
       </c>
       <c r="X72" s="0" t="inlineStr"/>
       <c r="Y72" s="0" t="inlineStr"/>
-      <c r="Z72" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z72" s="0" t="inlineStr"/>
       <c r="AA72" s="0" t="inlineStr"/>
       <c r="AB72" s="0" t="inlineStr">
         <is>
@@ -22924,11 +22848,7 @@
       </c>
       <c r="X79" s="0" t="inlineStr"/>
       <c r="Y79" s="0" t="inlineStr"/>
-      <c r="Z79" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z79" s="0" t="inlineStr"/>
       <c r="AA79" s="0" t="inlineStr"/>
       <c r="AB79" s="0" t="inlineStr">
         <is>
@@ -23226,7 +23146,11 @@
       </c>
       <c r="X81" s="0" t="inlineStr"/>
       <c r="Y81" s="0" t="inlineStr"/>
-      <c r="Z81" s="0" t="inlineStr"/>
+      <c r="Z81" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA81" s="0" t="inlineStr"/>
       <c r="AB81" s="0" t="inlineStr">
         <is>
@@ -23947,11 +23871,7 @@
           <t>2022-11-05 15-12-11</t>
         </is>
       </c>
-      <c r="X86" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X86" s="0" t="inlineStr"/>
       <c r="Y86" s="0" t="inlineStr"/>
       <c r="Z86" s="0" t="inlineStr"/>
       <c r="AA86" s="0" t="inlineStr"/>
@@ -25820,7 +25740,11 @@
       <c r="W99" s="0" t="inlineStr"/>
       <c r="X99" s="0" t="inlineStr"/>
       <c r="Y99" s="0" t="inlineStr"/>
-      <c r="Z99" s="0" t="inlineStr"/>
+      <c r="Z99" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA99" s="0" t="inlineStr"/>
       <c r="AB99" s="0" t="inlineStr"/>
       <c r="AC99" s="0" t="inlineStr"/>
@@ -25896,13 +25820,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ194"/>
+  <dimension ref="A1:AQ176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t>16.9.7708676+branch.releases-16-9.code.publictencent.content.release</t>
+          <t>16.13.7915903+branch.releases-16-13.code.publictencent.content.release</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -26796,11 +26720,7 @@
           <t>2024-09-30 07-29-57</t>
         </is>
       </c>
-      <c r="X6" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X6" s="0" t="inlineStr"/>
       <c r="Y6" s="0" t="inlineStr"/>
       <c r="Z6" s="0" t="inlineStr"/>
       <c r="AA6" s="0" t="inlineStr"/>
@@ -27064,13 +26984,21 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N8" s="0" t="inlineStr"/>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="O8" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="P8" s="0" t="inlineStr"/>
+      <c r="P8" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q8" s="0" t="inlineStr"/>
       <c r="R8" s="0" t="inlineStr"/>
       <c r="S8" s="0" t="inlineStr">
@@ -27094,17 +27022,9 @@
           <t>2024-11-21 23-33-50</t>
         </is>
       </c>
-      <c r="X8" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X8" s="0" t="inlineStr"/>
       <c r="Y8" s="0" t="inlineStr"/>
-      <c r="Z8" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z8" s="0" t="inlineStr"/>
       <c r="AA8" s="0" t="inlineStr"/>
       <c r="AB8" s="0" t="inlineStr">
         <is>
@@ -27251,7 +27171,11 @@
       </c>
       <c r="X9" s="0" t="inlineStr"/>
       <c r="Y9" s="0" t="inlineStr"/>
-      <c r="Z9" s="0" t="inlineStr"/>
+      <c r="Z9" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA9" s="0" t="inlineStr"/>
       <c r="AB9" s="0" t="inlineStr">
         <is>
@@ -27545,11 +27469,7 @@
       </c>
       <c r="X11" s="0" t="inlineStr"/>
       <c r="Y11" s="0" t="inlineStr"/>
-      <c r="Z11" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z11" s="0" t="inlineStr"/>
       <c r="AA11" s="0" t="inlineStr"/>
       <c r="AB11" s="0" t="inlineStr">
         <is>
@@ -27627,7 +27547,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>费德提克</t>
+          <t>远古恐惧</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -27845,11 +27765,7 @@
           <t>2023-08-04 00-53-36</t>
         </is>
       </c>
-      <c r="X13" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X13" s="0" t="inlineStr"/>
       <c r="Y13" s="0" t="inlineStr"/>
       <c r="Z13" s="0" t="inlineStr"/>
       <c r="AA13" s="0" t="inlineStr"/>
@@ -28145,11 +28061,7 @@
       </c>
       <c r="X15" s="0" t="inlineStr"/>
       <c r="Y15" s="0" t="inlineStr"/>
-      <c r="Z15" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z15" s="0" t="inlineStr"/>
       <c r="AA15" s="0" t="inlineStr"/>
       <c r="AB15" s="0" t="inlineStr">
         <is>
@@ -29303,7 +29215,11 @@
           <t>√</t>
         </is>
       </c>
-      <c r="P23" s="0" t="inlineStr"/>
+      <c r="P23" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q23" s="0" t="inlineStr"/>
       <c r="R23" s="0" t="inlineStr"/>
       <c r="S23" s="0" t="inlineStr">
@@ -30022,11 +29938,7 @@
       <c r="M28" s="0" t="inlineStr"/>
       <c r="N28" s="0" t="inlineStr"/>
       <c r="O28" s="0" t="inlineStr"/>
-      <c r="P28" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P28" s="0" t="inlineStr"/>
       <c r="Q28" s="0" t="inlineStr"/>
       <c r="R28" s="0" t="inlineStr">
         <is>
@@ -30054,11 +29966,7 @@
           <t>2023-10-03 15-43-15</t>
         </is>
       </c>
-      <c r="X28" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X28" s="0" t="inlineStr"/>
       <c r="Y28" s="0" t="inlineStr"/>
       <c r="Z28" s="0" t="inlineStr"/>
       <c r="AA28" s="0" t="inlineStr"/>
@@ -31518,7 +31426,11 @@
       </c>
       <c r="X38" s="0" t="inlineStr"/>
       <c r="Y38" s="0" t="inlineStr"/>
-      <c r="Z38" s="0" t="inlineStr"/>
+      <c r="Z38" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA38" s="0" t="inlineStr"/>
       <c r="AB38" s="0" t="inlineStr">
         <is>
@@ -31810,11 +31722,7 @@
           <t>2024-11-21 23-02-29</t>
         </is>
       </c>
-      <c r="X40" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X40" s="0" t="inlineStr"/>
       <c r="Y40" s="0" t="inlineStr"/>
       <c r="Z40" s="0" t="inlineStr">
         <is>
@@ -32118,11 +32026,7 @@
       </c>
       <c r="X42" s="0" t="inlineStr"/>
       <c r="Y42" s="0" t="inlineStr"/>
-      <c r="Z42" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z42" s="0" t="inlineStr"/>
       <c r="AA42" s="0" t="inlineStr"/>
       <c r="AB42" s="0" t="inlineStr">
         <is>
@@ -32378,11 +32282,7 @@
         </is>
       </c>
       <c r="O44" s="0" t="inlineStr"/>
-      <c r="P44" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P44" s="0" t="inlineStr"/>
       <c r="Q44" s="0" t="inlineStr"/>
       <c r="R44" s="0" t="inlineStr"/>
       <c r="S44" s="0" t="inlineStr">
@@ -32698,7 +32598,11 @@
       </c>
       <c r="X46" s="0" t="inlineStr"/>
       <c r="Y46" s="0" t="inlineStr"/>
-      <c r="Z46" s="0" t="inlineStr"/>
+      <c r="Z46" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA46" s="0" t="inlineStr"/>
       <c r="AB46" s="0" t="inlineStr">
         <is>
@@ -32845,7 +32749,11 @@
       </c>
       <c r="X47" s="0" t="inlineStr"/>
       <c r="Y47" s="0" t="inlineStr"/>
-      <c r="Z47" s="0" t="inlineStr"/>
+      <c r="Z47" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA47" s="0" t="inlineStr"/>
       <c r="AB47" s="0" t="inlineStr">
         <is>
@@ -33139,7 +33047,11 @@
       </c>
       <c r="X49" s="0" t="inlineStr"/>
       <c r="Y49" s="0" t="inlineStr"/>
-      <c r="Z49" s="0" t="inlineStr"/>
+      <c r="Z49" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA49" s="0" t="inlineStr"/>
       <c r="AB49" s="0" t="inlineStr">
         <is>
@@ -33290,11 +33202,7 @@
       </c>
       <c r="X50" s="0" t="inlineStr"/>
       <c r="Y50" s="0" t="inlineStr"/>
-      <c r="Z50" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z50" s="0" t="inlineStr"/>
       <c r="AA50" s="0" t="inlineStr"/>
       <c r="AB50" s="0" t="inlineStr">
         <is>
@@ -34472,11 +34380,7 @@
           <t>2020-02-21 21-04-16</t>
         </is>
       </c>
-      <c r="X58" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X58" s="0" t="inlineStr"/>
       <c r="Y58" s="0" t="inlineStr"/>
       <c r="Z58" s="0" t="inlineStr"/>
       <c r="AA58" s="0" t="inlineStr"/>
@@ -35037,7 +34941,11 @@
           <t>√</t>
         </is>
       </c>
-      <c r="Q62" s="0" t="inlineStr"/>
+      <c r="Q62" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="R62" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -35066,7 +34974,11 @@
       </c>
       <c r="X62" s="0" t="inlineStr"/>
       <c r="Y62" s="0" t="inlineStr"/>
-      <c r="Z62" s="0" t="inlineStr"/>
+      <c r="Z62" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA62" s="0" t="inlineStr"/>
       <c r="AB62" s="0" t="inlineStr">
         <is>
@@ -35358,11 +35270,7 @@
           <t>2024-07-06 23-55-14</t>
         </is>
       </c>
-      <c r="X64" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X64" s="0" t="inlineStr"/>
       <c r="Y64" s="0" t="inlineStr"/>
       <c r="Z64" s="0" t="inlineStr"/>
       <c r="AA64" s="0" t="inlineStr"/>
@@ -35633,11 +35541,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="Q66" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Q66" s="0" t="inlineStr"/>
       <c r="R66" s="0" t="inlineStr"/>
       <c r="S66" s="0" t="inlineStr">
         <is>
@@ -35813,7 +35717,11 @@
       </c>
       <c r="X67" s="0" t="inlineStr"/>
       <c r="Y67" s="0" t="inlineStr"/>
-      <c r="Z67" s="0" t="inlineStr"/>
+      <c r="Z67" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA67" s="0" t="inlineStr"/>
       <c r="AB67" s="0" t="inlineStr">
         <is>
@@ -35936,11 +35844,7 @@
         </is>
       </c>
       <c r="Q68" s="0" t="inlineStr"/>
-      <c r="R68" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="R68" s="0" t="inlineStr"/>
       <c r="S68" s="0" t="inlineStr">
         <is>
           <t>魔法伤害</t>
@@ -36562,13 +36466,13 @@
           <t>2020-01-27 22-43-05</t>
         </is>
       </c>
-      <c r="X72" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X72" s="0" t="inlineStr"/>
       <c r="Y72" s="0" t="inlineStr"/>
-      <c r="Z72" s="0" t="inlineStr"/>
+      <c r="Z72" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA72" s="0" t="inlineStr"/>
       <c r="AB72" s="0" t="inlineStr">
         <is>
@@ -37021,11 +36925,7 @@
       </c>
       <c r="X75" s="0" t="inlineStr"/>
       <c r="Y75" s="0" t="inlineStr"/>
-      <c r="Z75" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z75" s="0" t="inlineStr"/>
       <c r="AA75" s="0" t="inlineStr"/>
       <c r="AB75" s="0" t="inlineStr">
         <is>
@@ -37758,11 +37658,7 @@
           <t>2020-02-01 12-55-49</t>
         </is>
       </c>
-      <c r="X80" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X80" s="0" t="inlineStr"/>
       <c r="Y80" s="0" t="inlineStr"/>
       <c r="Z80" s="0" t="inlineStr">
         <is>
@@ -38201,11 +38097,7 @@
       </c>
       <c r="X83" s="0" t="inlineStr"/>
       <c r="Y83" s="0" t="inlineStr"/>
-      <c r="Z83" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z83" s="0" t="inlineStr"/>
       <c r="AA83" s="0" t="inlineStr"/>
       <c r="AB83" s="0" t="inlineStr">
         <is>
@@ -38322,7 +38214,11 @@
         </is>
       </c>
       <c r="O84" s="0" t="inlineStr"/>
-      <c r="P84" s="0" t="inlineStr"/>
+      <c r="P84" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q84" s="0" t="inlineStr"/>
       <c r="R84" s="0" t="inlineStr"/>
       <c r="S84" s="0" t="inlineStr">
@@ -38791,11 +38687,7 @@
           <t>2021-12-23 20-26-31</t>
         </is>
       </c>
-      <c r="X87" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X87" s="0" t="inlineStr"/>
       <c r="Y87" s="0" t="inlineStr"/>
       <c r="Z87" s="0" t="inlineStr"/>
       <c r="AA87" s="0" t="inlineStr"/>
@@ -39089,11 +38981,7 @@
           <t>2024-07-17 19-18-08</t>
         </is>
       </c>
-      <c r="X89" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X89" s="0" t="inlineStr"/>
       <c r="Y89" s="0" t="inlineStr"/>
       <c r="Z89" s="0" t="inlineStr"/>
       <c r="AA89" s="0" t="inlineStr"/>
@@ -39497,11 +39385,7 @@
       <c r="L92" s="0" t="inlineStr"/>
       <c r="M92" s="0" t="inlineStr"/>
       <c r="N92" s="0" t="inlineStr"/>
-      <c r="O92" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="O92" s="0" t="inlineStr"/>
       <c r="P92" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -39532,7 +39416,11 @@
       </c>
       <c r="X92" s="0" t="inlineStr"/>
       <c r="Y92" s="0" t="inlineStr"/>
-      <c r="Z92" s="0" t="inlineStr"/>
+      <c r="Z92" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA92" s="0" t="inlineStr"/>
       <c r="AB92" s="0" t="inlineStr">
         <is>
@@ -40267,7 +40155,11 @@
       </c>
       <c r="X97" s="0" t="inlineStr"/>
       <c r="Y97" s="0" t="inlineStr"/>
-      <c r="Z97" s="0" t="inlineStr"/>
+      <c r="Z97" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA97" s="0" t="inlineStr"/>
       <c r="AB97" s="0" t="inlineStr">
         <is>
@@ -40378,11 +40270,7 @@
           <t>√</t>
         </is>
       </c>
-      <c r="N98" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N98" s="0" t="inlineStr"/>
       <c r="O98" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -40414,11 +40302,7 @@
       </c>
       <c r="X98" s="0" t="inlineStr"/>
       <c r="Y98" s="0" t="inlineStr"/>
-      <c r="Z98" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z98" s="0" t="inlineStr"/>
       <c r="AA98" s="0" t="inlineStr"/>
       <c r="AB98" s="0" t="inlineStr">
         <is>
@@ -40559,11 +40443,7 @@
           <t>2024-09-11 02-44-10</t>
         </is>
       </c>
-      <c r="X99" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X99" s="0" t="inlineStr"/>
       <c r="Y99" s="0" t="inlineStr"/>
       <c r="Z99" s="0" t="inlineStr"/>
       <c r="AA99" s="0" t="inlineStr"/>
@@ -41002,7 +40882,11 @@
       </c>
       <c r="X102" s="0" t="inlineStr"/>
       <c r="Y102" s="0" t="inlineStr"/>
-      <c r="Z102" s="0" t="inlineStr"/>
+      <c r="Z102" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA102" s="0" t="inlineStr"/>
       <c r="AB102" s="0" t="inlineStr">
         <is>
@@ -41590,11 +41474,7 @@
       </c>
       <c r="X106" s="0" t="inlineStr"/>
       <c r="Y106" s="0" t="inlineStr"/>
-      <c r="Z106" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z106" s="0" t="inlineStr"/>
       <c r="AA106" s="0" t="inlineStr"/>
       <c r="AB106" s="0" t="inlineStr">
         <is>
@@ -41888,11 +41768,7 @@
       </c>
       <c r="X108" s="0" t="inlineStr"/>
       <c r="Y108" s="0" t="inlineStr"/>
-      <c r="Z108" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z108" s="0" t="inlineStr"/>
       <c r="AA108" s="0" t="inlineStr"/>
       <c r="AB108" s="0" t="inlineStr">
         <is>
@@ -42008,7 +41884,11 @@
           <t>√</t>
         </is>
       </c>
-      <c r="O109" s="0" t="inlineStr"/>
+      <c r="O109" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="P109" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -42037,11 +41917,7 @@
           <t>2024-09-11 02-03-12</t>
         </is>
       </c>
-      <c r="X109" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X109" s="0" t="inlineStr"/>
       <c r="Y109" s="0" t="inlineStr"/>
       <c r="Z109" s="0" t="inlineStr"/>
       <c r="AA109" s="0" t="inlineStr"/>
@@ -42909,7 +42785,11 @@
       </c>
       <c r="X115" s="0" t="inlineStr"/>
       <c r="Y115" s="0" t="inlineStr"/>
-      <c r="Z115" s="0" t="inlineStr"/>
+      <c r="Z115" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA115" s="0" t="inlineStr"/>
       <c r="AB115" s="0" t="inlineStr">
         <is>
@@ -43791,11 +43671,7 @@
       </c>
       <c r="X121" s="0" t="inlineStr"/>
       <c r="Y121" s="0" t="inlineStr"/>
-      <c r="Z121" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z121" s="0" t="inlineStr"/>
       <c r="AA121" s="0" t="inlineStr"/>
       <c r="AB121" s="0" t="inlineStr">
         <is>
@@ -44792,11 +44668,7 @@
       </c>
       <c r="X128" s="0" t="inlineStr"/>
       <c r="Y128" s="0" t="inlineStr"/>
-      <c r="Z128" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z128" s="0" t="inlineStr"/>
       <c r="AA128" s="0" t="inlineStr"/>
       <c r="AB128" s="0" t="inlineStr">
         <is>
@@ -45660,11 +45532,7 @@
           <t>2022-11-05 15-12-11</t>
         </is>
       </c>
-      <c r="X134" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X134" s="0" t="inlineStr"/>
       <c r="Y134" s="0" t="inlineStr"/>
       <c r="Z134" s="0" t="inlineStr"/>
       <c r="AA134" s="0" t="inlineStr"/>
@@ -45948,11 +45816,7 @@
       </c>
       <c r="X136" s="0" t="inlineStr"/>
       <c r="Y136" s="0" t="inlineStr"/>
-      <c r="Z136" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="Z136" s="0" t="inlineStr"/>
       <c r="AA136" s="0" t="inlineStr"/>
       <c r="AB136" s="0" t="inlineStr">
         <is>
@@ -48528,11 +48392,7 @@
           <t>2024-09-11 02-44-10</t>
         </is>
       </c>
-      <c r="X154" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="X154" s="0" t="inlineStr"/>
       <c r="Y154" s="0" t="inlineStr"/>
       <c r="Z154" s="0" t="inlineStr"/>
       <c r="AA154" s="0" t="inlineStr"/>
@@ -49883,21 +49743,21 @@
         <v>162</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>875</v>
+        <v>805</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>腕豪</t>
+          <t>灰烬驱魔人</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>瑟提</t>
+          <t>洛克</t>
         </is>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
-          <t>Sett</t>
+          <t>Locke</t>
         </is>
       </c>
       <c r="F164" s="0" t="inlineStr">
@@ -49905,64 +49765,52 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G164" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="H164" s="0" t="inlineStr"/>
-      <c r="I164" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J164" s="0" t="inlineStr"/>
+      <c r="G164" s="0" t="inlineStr"/>
+      <c r="H164" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="I164" s="0" t="inlineStr"/>
+      <c r="J164" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K164" s="0" t="inlineStr"/>
       <c r="L164" s="0" t="inlineStr"/>
-      <c r="M164" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N164" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O164" s="0" t="inlineStr"/>
-      <c r="P164" s="0" t="inlineStr"/>
+      <c r="M164" s="0" t="inlineStr"/>
+      <c r="N164" s="0" t="inlineStr"/>
+      <c r="O164" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="P164" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q164" s="0" t="inlineStr"/>
       <c r="R164" s="0" t="inlineStr"/>
       <c r="S164" s="0" t="inlineStr">
         <is>
-          <t>物理伤害</t>
+          <t>魔法伤害</t>
         </is>
       </c>
       <c r="T164" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U164" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="V164" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="W164" s="0" t="inlineStr">
-        <is>
-          <t>2023-04-05 15-55-07</t>
-        </is>
-      </c>
+      <c r="V164" s="0" t="inlineStr"/>
+      <c r="W164" s="0" t="inlineStr"/>
       <c r="X164" s="0" t="inlineStr"/>
       <c r="Y164" s="0" t="inlineStr"/>
       <c r="Z164" s="0" t="inlineStr"/>
       <c r="AA164" s="0" t="inlineStr"/>
-      <c r="AB164" s="0" t="inlineStr">
-        <is>
-          <t>2023-04-05 15-55-07</t>
-        </is>
-      </c>
+      <c r="AB164" s="0" t="inlineStr"/>
       <c r="AC164" s="0" t="inlineStr"/>
       <c r="AD164" s="0" t="n">
         <v>0</v>
@@ -49971,57 +49819,57 @@
       <c r="AF164" s="0" t="inlineStr"/>
       <c r="AG164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/875.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/805.png</t>
         </is>
       </c>
       <c r="AH164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Sett/Skins/Base/SettLoadscreen.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Locke/Skins/Base/LockeLoadScreen_0.Locke.jpg</t>
         </is>
       </c>
       <c r="AI164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Sett/Skins/Base/Images/sett_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Locke/Skins/Base/Images/Locke_splash_centered_0.Locke.jpg</t>
         </is>
       </c>
       <c r="AJ164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/875.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/805.ogg</t>
         </is>
       </c>
       <c r="AK164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/875.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/805.ogg</t>
         </is>
       </c>
       <c r="AL164" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/875.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/805.ogg</t>
         </is>
       </c>
       <c r="AM164" s="0" t="inlineStr">
         <is>
-          <t>沙场豪情</t>
+          <t>圣银穿心</t>
         </is>
       </c>
       <c r="AN164" s="0" t="inlineStr">
         <is>
-          <t>屈人之威</t>
+          <t>伏魔三钉</t>
         </is>
       </c>
       <c r="AO164" s="0" t="inlineStr">
         <is>
-          <t>蓄意轰拳</t>
+          <t>灵焰仪式</t>
         </is>
       </c>
       <c r="AP164" s="0" t="inlineStr">
         <is>
-          <t>强手裂颅</t>
+          <t>灰猎无影</t>
         </is>
       </c>
       <c r="AQ164" s="0" t="inlineStr">
         <is>
-          <t>叹为观止</t>
+          <t>万魔狱</t>
         </is>
       </c>
     </row>
@@ -50030,21 +49878,21 @@
         <v>163</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>含羞蓓蕾</t>
+          <t>腕豪</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
         <is>
-          <t>莉莉娅</t>
+          <t>瑟提</t>
         </is>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
-          <t>Lillia</t>
+          <t>Sett</t>
         </is>
       </c>
       <c r="F165" s="0" t="inlineStr">
@@ -50063,30 +49911,30 @@
           <t>√</t>
         </is>
       </c>
-      <c r="J165" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="J165" s="0" t="inlineStr"/>
       <c r="K165" s="0" t="inlineStr"/>
       <c r="L165" s="0" t="inlineStr"/>
-      <c r="M165" s="0" t="inlineStr"/>
-      <c r="N165" s="0" t="inlineStr"/>
-      <c r="O165" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="M165" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="N165" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="O165" s="0" t="inlineStr"/>
       <c r="P165" s="0" t="inlineStr"/>
       <c r="Q165" s="0" t="inlineStr"/>
       <c r="R165" s="0" t="inlineStr"/>
       <c r="S165" s="0" t="inlineStr">
         <is>
-          <t>魔法伤害</t>
+          <t>物理伤害</t>
         </is>
       </c>
       <c r="T165" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U165" s="0" t="n">
         <v>2</v>
@@ -50098,7 +49946,7 @@
       </c>
       <c r="W165" s="0" t="inlineStr">
         <is>
-          <t>2024-08-22 02-12-46</t>
+          <t>2023-04-05 15-55-07</t>
         </is>
       </c>
       <c r="X165" s="0" t="inlineStr"/>
@@ -50107,7 +49955,7 @@
       <c r="AA165" s="0" t="inlineStr"/>
       <c r="AB165" s="0" t="inlineStr">
         <is>
-          <t>2024-08-22 02-12-46</t>
+          <t>2023-04-05 15-55-07</t>
         </is>
       </c>
       <c r="AC165" s="0" t="inlineStr"/>
@@ -50118,57 +49966,57 @@
       <c r="AF165" s="0" t="inlineStr"/>
       <c r="AG165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/876.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/875.png</t>
         </is>
       </c>
       <c r="AH165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Lillia/Skins/Base/LilliaLoadscreen.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Sett/Skins/Base/SettLoadscreen.jpg</t>
         </is>
       </c>
       <c r="AI165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Lillia/Skins/Base/Images/lillia_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Sett/Skins/Base/Images/sett_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/876.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/875.ogg</t>
         </is>
       </c>
       <c r="AK165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/876.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/875.ogg</t>
         </is>
       </c>
       <c r="AL165" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/876.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/875.ogg</t>
         </is>
       </c>
       <c r="AM165" s="0" t="inlineStr">
         <is>
-          <t>梦满枝</t>
+          <t>沙场豪情</t>
         </is>
       </c>
       <c r="AN165" s="0" t="inlineStr">
         <is>
-          <t>飞花挞</t>
+          <t>屈人之威</t>
         </is>
       </c>
       <c r="AO165" s="0" t="inlineStr">
         <is>
-          <t>惊惶木</t>
+          <t>蓄意轰拳</t>
         </is>
       </c>
       <c r="AP165" s="0" t="inlineStr">
         <is>
-          <t>流涡种</t>
+          <t>强手裂颅</t>
         </is>
       </c>
       <c r="AQ165" s="0" t="inlineStr">
         <is>
-          <t>夜阑谣</t>
+          <t>叹为观止</t>
         </is>
       </c>
     </row>
@@ -50177,21 +50025,21 @@
         <v>164</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>灵罗娃娃</t>
+          <t>含羞蓓蕾</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
-          <t>格温</t>
+          <t>莉莉娅</t>
         </is>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Lillia</t>
         </is>
       </c>
       <c r="F166" s="0" t="inlineStr">
@@ -50199,32 +50047,32 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G166" s="0" t="inlineStr"/>
+      <c r="G166" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="H166" s="0" t="inlineStr"/>
       <c r="I166" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="J166" s="0" t="inlineStr"/>
+      <c r="J166" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K166" s="0" t="inlineStr"/>
       <c r="L166" s="0" t="inlineStr"/>
       <c r="M166" s="0" t="inlineStr"/>
-      <c r="N166" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N166" s="0" t="inlineStr"/>
       <c r="O166" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="P166" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P166" s="0" t="inlineStr"/>
       <c r="Q166" s="0" t="inlineStr"/>
       <c r="R166" s="0" t="inlineStr"/>
       <c r="S166" s="0" t="inlineStr">
@@ -50233,7 +50081,7 @@
         </is>
       </c>
       <c r="T166" s="0" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U166" s="0" t="n">
         <v>2</v>
@@ -50245,7 +50093,7 @@
       </c>
       <c r="W166" s="0" t="inlineStr">
         <is>
-          <t>2024-09-11 02-03-13</t>
+          <t>2024-08-22 02-12-46</t>
         </is>
       </c>
       <c r="X166" s="0" t="inlineStr"/>
@@ -50254,7 +50102,7 @@
       <c r="AA166" s="0" t="inlineStr"/>
       <c r="AB166" s="0" t="inlineStr">
         <is>
-          <t>2024-09-11 02-03-13</t>
+          <t>2024-08-22 02-12-46</t>
         </is>
       </c>
       <c r="AC166" s="0" t="inlineStr"/>
@@ -50265,57 +50113,57 @@
       <c r="AF166" s="0" t="inlineStr"/>
       <c r="AG166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/887.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/876.png</t>
         </is>
       </c>
       <c r="AH166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Gwen/Skins/Base/GwenLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Lillia/Skins/Base/LilliaLoadscreen.jpg</t>
         </is>
       </c>
       <c r="AI166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Gwen/Skins/Base/Images/gwen_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Lillia/Skins/Base/Images/lillia_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/887.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/876.ogg</t>
         </is>
       </c>
       <c r="AK166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/887.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/876.ogg</t>
         </is>
       </c>
       <c r="AL166" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/887.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/876.ogg</t>
         </is>
       </c>
       <c r="AM166" s="0" t="inlineStr">
         <is>
-          <t>千穿百孔</t>
+          <t>梦满枝</t>
         </is>
       </c>
       <c r="AN166" s="0" t="inlineStr">
         <is>
-          <t>快刀剪乱</t>
+          <t>飞花挞</t>
         </is>
       </c>
       <c r="AO166" s="0" t="inlineStr">
         <is>
-          <t>丝缕缠流</t>
+          <t>惊惶木</t>
         </is>
       </c>
       <c r="AP166" s="0" t="inlineStr">
         <is>
-          <t>断续疾走</t>
+          <t>流涡种</t>
         </is>
       </c>
       <c r="AQ166" s="0" t="inlineStr">
         <is>
-          <t>引针簇射</t>
+          <t>夜阑谣</t>
         </is>
       </c>
     </row>
@@ -50324,21 +50172,21 @@
         <v>165</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>炼金男爵</t>
+          <t>灵罗娃娃</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>烈娜塔 · 戈拉斯克</t>
+          <t>格温</t>
         </is>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="F167" s="0" t="inlineStr">
@@ -50346,41 +50194,41 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G167" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="G167" s="0" t="inlineStr"/>
       <c r="H167" s="0" t="inlineStr"/>
-      <c r="I167" s="0" t="inlineStr"/>
-      <c r="J167" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="I167" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="J167" s="0" t="inlineStr"/>
       <c r="K167" s="0" t="inlineStr"/>
-      <c r="L167" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="L167" s="0" t="inlineStr"/>
       <c r="M167" s="0" t="inlineStr"/>
-      <c r="N167" s="0" t="inlineStr"/>
-      <c r="O167" s="0" t="inlineStr"/>
-      <c r="P167" s="0" t="inlineStr"/>
+      <c r="N167" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="O167" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="P167" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="Q167" s="0" t="inlineStr"/>
-      <c r="R167" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="R167" s="0" t="inlineStr"/>
       <c r="S167" s="0" t="inlineStr">
         <is>
           <t>魔法伤害</t>
         </is>
       </c>
       <c r="T167" s="0" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U167" s="0" t="n">
         <v>2</v>
@@ -50392,7 +50240,7 @@
       </c>
       <c r="W167" s="0" t="inlineStr">
         <is>
-          <t>2022-02-19 16-19-34</t>
+          <t>2024-09-11 02-03-13</t>
         </is>
       </c>
       <c r="X167" s="0" t="inlineStr"/>
@@ -50401,7 +50249,7 @@
       <c r="AA167" s="0" t="inlineStr"/>
       <c r="AB167" s="0" t="inlineStr">
         <is>
-          <t>2022-02-19 16-19-34</t>
+          <t>2024-09-11 02-03-13</t>
         </is>
       </c>
       <c r="AC167" s="0" t="inlineStr"/>
@@ -50412,57 +50260,57 @@
       <c r="AF167" s="0" t="inlineStr"/>
       <c r="AG167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/888.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/887.png</t>
         </is>
       </c>
       <c r="AH167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Renata/Skins/Base/RenataLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Gwen/Skins/Base/GwenLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Renata/Skins/Base/Images/Renata_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Gwen/Skins/Base/Images/gwen_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/888.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/887.ogg</t>
         </is>
       </c>
       <c r="AK167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/888.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/887.ogg</t>
         </is>
       </c>
       <c r="AL167" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/888.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/887.ogg</t>
         </is>
       </c>
       <c r="AM167" s="0" t="inlineStr">
         <is>
-          <t>物尽其用</t>
+          <t>千穿百孔</t>
         </is>
       </c>
       <c r="AN167" s="0" t="inlineStr">
         <is>
-          <t>铁腕竞合</t>
+          <t>快刀剪乱</t>
         </is>
       </c>
       <c r="AO167" s="0" t="inlineStr">
         <is>
-          <t>及时救难</t>
+          <t>丝缕缠流</t>
         </is>
       </c>
       <c r="AP167" s="0" t="inlineStr">
         <is>
-          <t>忠诚激励</t>
+          <t>断续疾走</t>
         </is>
       </c>
       <c r="AQ167" s="0" t="inlineStr">
         <is>
-          <t>恶意收购</t>
+          <t>引针簇射</t>
         </is>
       </c>
     </row>
@@ -50471,21 +50319,21 @@
         <v>166</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>双界灵兔</t>
+          <t>炼金男爵</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>阿萝拉</t>
+          <t>烈娜塔 · 戈拉斯克</t>
         </is>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="F168" s="0" t="inlineStr">
@@ -50493,12 +50341,12 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G168" s="0" t="inlineStr"/>
-      <c r="H168" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="G168" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="H168" s="0" t="inlineStr"/>
       <c r="I168" s="0" t="inlineStr"/>
       <c r="J168" s="0" t="inlineStr">
         <is>
@@ -50506,28 +50354,28 @@
         </is>
       </c>
       <c r="K168" s="0" t="inlineStr"/>
-      <c r="L168" s="0" t="inlineStr"/>
+      <c r="L168" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="M168" s="0" t="inlineStr"/>
-      <c r="N168" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N168" s="0" t="inlineStr"/>
       <c r="O168" s="0" t="inlineStr"/>
-      <c r="P168" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P168" s="0" t="inlineStr"/>
       <c r="Q168" s="0" t="inlineStr"/>
-      <c r="R168" s="0" t="inlineStr"/>
+      <c r="R168" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="S168" s="0" t="inlineStr">
         <is>
           <t>魔法伤害</t>
         </is>
       </c>
       <c r="T168" s="0" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U168" s="0" t="n">
         <v>2</v>
@@ -50539,7 +50387,7 @@
       </c>
       <c r="W168" s="0" t="inlineStr">
         <is>
-          <t>2024-11-21 23-15-56</t>
+          <t>2022-02-19 16-19-34</t>
         </is>
       </c>
       <c r="X168" s="0" t="inlineStr"/>
@@ -50548,7 +50396,7 @@
       <c r="AA168" s="0" t="inlineStr"/>
       <c r="AB168" s="0" t="inlineStr">
         <is>
-          <t>2024-11-21 23-15-56</t>
+          <t>2022-02-19 16-19-34</t>
         </is>
       </c>
       <c r="AC168" s="0" t="inlineStr"/>
@@ -50559,57 +50407,57 @@
       <c r="AF168" s="0" t="inlineStr"/>
       <c r="AG168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/893.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/888.png</t>
         </is>
       </c>
       <c r="AH168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Aurora/Skins/Base/AuroraLoadScreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Renata/Skins/Base/RenataLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Aurora/Skins/Base/Images/Aurora_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Renata/Skins/Base/Images/Renata_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/893.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/888.ogg</t>
         </is>
       </c>
       <c r="AK168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/893.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/888.ogg</t>
         </is>
       </c>
       <c r="AL168" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/893.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/888.ogg</t>
         </is>
       </c>
       <c r="AM168" s="0" t="inlineStr">
         <is>
-          <t>驱灵奇术</t>
+          <t>物尽其用</t>
         </is>
       </c>
       <c r="AN168" s="0" t="inlineStr">
         <is>
-          <t>飞去来咒</t>
+          <t>铁腕竞合</t>
         </is>
       </c>
       <c r="AO168" s="0" t="inlineStr">
         <is>
-          <t>灵纱洞开</t>
+          <t>及时救难</t>
         </is>
       </c>
       <c r="AP168" s="0" t="inlineStr">
         <is>
-          <t>怪奇喷涌</t>
+          <t>忠诚激励</t>
         </is>
       </c>
       <c r="AQ168" s="0" t="inlineStr">
         <is>
-          <t>双界合一</t>
+          <t>恶意收购</t>
         </is>
       </c>
     </row>
@@ -50618,21 +50466,21 @@
         <v>167</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>不羁之悦</t>
+          <t>双界灵兔</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>尼菈</t>
+          <t>阿萝拉</t>
         </is>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
-          <t>Nilah</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F169" s="0" t="inlineStr">
@@ -50646,34 +50494,38 @@
           <t>√</t>
         </is>
       </c>
-      <c r="I169" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J169" s="0" t="inlineStr"/>
+      <c r="I169" s="0" t="inlineStr"/>
+      <c r="J169" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K169" s="0" t="inlineStr"/>
       <c r="L169" s="0" t="inlineStr"/>
       <c r="M169" s="0" t="inlineStr"/>
-      <c r="N169" s="0" t="inlineStr"/>
+      <c r="N169" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="O169" s="0" t="inlineStr"/>
-      <c r="P169" s="0" t="inlineStr"/>
-      <c r="Q169" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P169" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Q169" s="0" t="inlineStr"/>
       <c r="R169" s="0" t="inlineStr"/>
       <c r="S169" s="0" t="inlineStr">
         <is>
-          <t>物理伤害</t>
+          <t>魔法伤害</t>
         </is>
       </c>
       <c r="T169" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U169" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V169" s="0" t="inlineStr">
         <is>
@@ -50682,7 +50534,7 @@
       </c>
       <c r="W169" s="0" t="inlineStr">
         <is>
-          <t>2024-09-11 02-44-10</t>
+          <t>2024-11-21 23-15-56</t>
         </is>
       </c>
       <c r="X169" s="0" t="inlineStr"/>
@@ -50691,7 +50543,7 @@
       <c r="AA169" s="0" t="inlineStr"/>
       <c r="AB169" s="0" t="inlineStr">
         <is>
-          <t>2024-09-11 02-44-10</t>
+          <t>2024-11-21 23-15-56</t>
         </is>
       </c>
       <c r="AC169" s="0" t="inlineStr"/>
@@ -50702,57 +50554,57 @@
       <c r="AF169" s="0" t="inlineStr"/>
       <c r="AG169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/895.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/893.png</t>
         </is>
       </c>
       <c r="AH169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Nilah/Skins/Base/NilahLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Aurora/Skins/Base/AuroraLoadScreen_0.jpg</t>
         </is>
       </c>
       <c r="AI169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Nilah/Skins/Base/Images/Nilah_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Aurora/Skins/Base/Images/Aurora_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/895.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/893.ogg</t>
         </is>
       </c>
       <c r="AK169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/895.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/893.ogg</t>
         </is>
       </c>
       <c r="AL169" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/895.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/893.ogg</t>
         </is>
       </c>
       <c r="AM169" s="0" t="inlineStr">
         <is>
-          <t>喜色川流</t>
+          <t>驱灵奇术</t>
         </is>
       </c>
       <c r="AN169" s="0" t="inlineStr">
         <is>
-          <t>游刃万变</t>
+          <t>飞去来咒</t>
         </is>
       </c>
       <c r="AO169" s="0" t="inlineStr">
         <is>
-          <t>轻纱飞漾</t>
+          <t>灵纱洞开</t>
         </is>
       </c>
       <c r="AP169" s="0" t="inlineStr">
         <is>
-          <t>纵情逐流</t>
+          <t>怪奇喷涌</t>
         </is>
       </c>
       <c r="AQ169" s="0" t="inlineStr">
         <is>
-          <t>神恩激荡</t>
+          <t>双界合一</t>
         </is>
       </c>
     </row>
@@ -50761,21 +50613,21 @@
         <v>168</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>纳祖芒荣耀</t>
+          <t>不羁之悦</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
         <is>
-          <t>奎桑提</t>
+          <t>尼菈</t>
         </is>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
-          <t>KSante</t>
+          <t>Nilah</t>
         </is>
       </c>
       <c r="F170" s="0" t="inlineStr">
@@ -50784,7 +50636,11 @@
         </is>
       </c>
       <c r="G170" s="0" t="inlineStr"/>
-      <c r="H170" s="0" t="inlineStr"/>
+      <c r="H170" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="I170" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -50793,19 +50649,15 @@
       <c r="J170" s="0" t="inlineStr"/>
       <c r="K170" s="0" t="inlineStr"/>
       <c r="L170" s="0" t="inlineStr"/>
-      <c r="M170" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N170" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="M170" s="0" t="inlineStr"/>
+      <c r="N170" s="0" t="inlineStr"/>
       <c r="O170" s="0" t="inlineStr"/>
       <c r="P170" s="0" t="inlineStr"/>
-      <c r="Q170" s="0" t="inlineStr"/>
+      <c r="Q170" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="R170" s="0" t="inlineStr"/>
       <c r="S170" s="0" t="inlineStr">
         <is>
@@ -50825,7 +50677,7 @@
       </c>
       <c r="W170" s="0" t="inlineStr">
         <is>
-          <t>2024-07-17 19-18-39</t>
+          <t>2024-09-11 02-44-10</t>
         </is>
       </c>
       <c r="X170" s="0" t="inlineStr"/>
@@ -50834,7 +50686,7 @@
       <c r="AA170" s="0" t="inlineStr"/>
       <c r="AB170" s="0" t="inlineStr">
         <is>
-          <t>2024-07-17 19-18-39</t>
+          <t>2024-09-11 02-44-10</t>
         </is>
       </c>
       <c r="AC170" s="0" t="inlineStr"/>
@@ -50845,57 +50697,57 @@
       <c r="AF170" s="0" t="inlineStr"/>
       <c r="AG170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/897.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/895.png</t>
         </is>
       </c>
       <c r="AH170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/KSante/Skins/Base/KSanteLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Nilah/Skins/Base/NilahLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/KSante/Skins/Base/Images/KSante_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Nilah/Skins/Base/Images/Nilah_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/897.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/895.ogg</t>
         </is>
       </c>
       <c r="AK170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/897.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/895.ogg</t>
         </is>
       </c>
       <c r="AL170" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/897.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/895.ogg</t>
         </is>
       </c>
       <c r="AM170" s="0" t="inlineStr">
         <is>
-          <t>血性本能</t>
+          <t>喜色川流</t>
         </is>
       </c>
       <c r="AN170" s="0" t="inlineStr">
         <is>
-          <t>无双陀斧</t>
+          <t>游刃万变</t>
         </is>
       </c>
       <c r="AO170" s="0" t="inlineStr">
         <is>
-          <t>辟路先锋</t>
+          <t>轻纱飞漾</t>
         </is>
       </c>
       <c r="AP170" s="0" t="inlineStr">
         <is>
-          <t>大步驰援</t>
+          <t>纵情逐流</t>
         </is>
       </c>
       <c r="AQ170" s="0" t="inlineStr">
         <is>
-          <t>傲岸雄姿</t>
+          <t>神恩激荡</t>
         </is>
       </c>
     </row>
@@ -50904,21 +50756,21 @@
         <v>169</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>炽炎雏龙</t>
+          <t>纳祖芒荣耀</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>斯莫德</t>
+          <t>奎桑提</t>
         </is>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
-          <t>Smolder</t>
+          <t>KSante</t>
         </is>
       </c>
       <c r="F171" s="0" t="inlineStr">
@@ -50926,37 +50778,29 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G171" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="G171" s="0" t="inlineStr"/>
       <c r="H171" s="0" t="inlineStr"/>
-      <c r="I171" s="0" t="inlineStr"/>
-      <c r="J171" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K171" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="I171" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="J171" s="0" t="inlineStr"/>
+      <c r="K171" s="0" t="inlineStr"/>
       <c r="L171" s="0" t="inlineStr"/>
-      <c r="M171" s="0" t="inlineStr"/>
-      <c r="N171" s="0" t="inlineStr"/>
+      <c r="M171" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="N171" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="O171" s="0" t="inlineStr"/>
-      <c r="P171" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q171" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P171" s="0" t="inlineStr"/>
+      <c r="Q171" s="0" t="inlineStr"/>
       <c r="R171" s="0" t="inlineStr"/>
       <c r="S171" s="0" t="inlineStr">
         <is>
@@ -50964,10 +50808,10 @@
         </is>
       </c>
       <c r="T171" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U171" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V171" s="0" t="inlineStr">
         <is>
@@ -50976,7 +50820,7 @@
       </c>
       <c r="W171" s="0" t="inlineStr">
         <is>
-          <t>2024-02-19 11-42-16</t>
+          <t>2024-07-17 19-18-39</t>
         </is>
       </c>
       <c r="X171" s="0" t="inlineStr"/>
@@ -50985,7 +50829,7 @@
       <c r="AA171" s="0" t="inlineStr"/>
       <c r="AB171" s="0" t="inlineStr">
         <is>
-          <t>2024-02-19 11-42-16</t>
+          <t>2024-07-17 19-18-39</t>
         </is>
       </c>
       <c r="AC171" s="0" t="inlineStr"/>
@@ -50996,57 +50840,57 @@
       <c r="AF171" s="0" t="inlineStr"/>
       <c r="AG171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/901.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/897.png</t>
         </is>
       </c>
       <c r="AH171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Smolder/Skins/Base/SmolderLoadScreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/KSante/Skins/Base/KSanteLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Smolder/Skins/Base/Images/Smolder_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/KSante/Skins/Base/Images/KSante_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/901.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/897.ogg</t>
         </is>
       </c>
       <c r="AK171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/901.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/897.ogg</t>
         </is>
       </c>
       <c r="AL171" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/901.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/897.ogg</t>
         </is>
       </c>
       <c r="AM171" s="0" t="inlineStr">
         <is>
-          <t>龙之研习</t>
+          <t>血性本能</t>
         </is>
       </c>
       <c r="AN171" s="0" t="inlineStr">
         <is>
-          <t>超级灼热龙息</t>
+          <t>无双陀斧</t>
         </is>
       </c>
       <c r="AO171" s="0" t="inlineStr">
         <is>
-          <t>阿嚏！</t>
+          <t>辟路先锋</t>
         </is>
       </c>
       <c r="AP171" s="0" t="inlineStr">
         <is>
-          <t>扑棱，扑棱，扑棱！</t>
+          <t>大步驰援</t>
         </is>
       </c>
       <c r="AQ171" s="0" t="inlineStr">
         <is>
-          <t>妈----！</t>
+          <t>傲岸雄姿</t>
         </is>
       </c>
     </row>
@@ -51055,21 +50899,21 @@
         <v>170</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>明烛</t>
+          <t>炽炎雏龙</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>米利欧</t>
+          <t>斯莫德</t>
         </is>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
-          <t>Milio</t>
+          <t>Smolder</t>
         </is>
       </c>
       <c r="F172" s="0" t="inlineStr">
@@ -51089,29 +50933,33 @@
           <t>√</t>
         </is>
       </c>
-      <c r="K172" s="0" t="inlineStr"/>
-      <c r="L172" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="K172" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="L172" s="0" t="inlineStr"/>
       <c r="M172" s="0" t="inlineStr"/>
       <c r="N172" s="0" t="inlineStr"/>
       <c r="O172" s="0" t="inlineStr"/>
-      <c r="P172" s="0" t="inlineStr"/>
-      <c r="Q172" s="0" t="inlineStr"/>
-      <c r="R172" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="P172" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Q172" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="R172" s="0" t="inlineStr"/>
       <c r="S172" s="0" t="inlineStr">
         <is>
-          <t>魔法伤害</t>
+          <t>物理伤害</t>
         </is>
       </c>
       <c r="T172" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U172" s="0" t="n">
         <v>1</v>
@@ -51123,7 +50971,7 @@
       </c>
       <c r="W172" s="0" t="inlineStr">
         <is>
-          <t>2024-07-06 23-54-41</t>
+          <t>2024-02-19 11-42-16</t>
         </is>
       </c>
       <c r="X172" s="0" t="inlineStr"/>
@@ -51132,7 +50980,7 @@
       <c r="AA172" s="0" t="inlineStr"/>
       <c r="AB172" s="0" t="inlineStr">
         <is>
-          <t>2024-07-06 23-54-41</t>
+          <t>2024-02-19 11-42-16</t>
         </is>
       </c>
       <c r="AC172" s="0" t="inlineStr"/>
@@ -51143,57 +50991,57 @@
       <c r="AF172" s="0" t="inlineStr"/>
       <c r="AG172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/902.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/901.png</t>
         </is>
       </c>
       <c r="AH172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Milio/Skins/Base/MilioLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Smolder/Skins/Base/SmolderLoadScreen_0.jpg</t>
         </is>
       </c>
       <c r="AI172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Milio/Skins/Base/Images/Milio_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Smolder/Skins/Base/Images/Smolder_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/902.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/901.ogg</t>
         </is>
       </c>
       <c r="AK172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/902.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/901.ogg</t>
         </is>
       </c>
       <c r="AL172" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/902.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/901.ogg</t>
         </is>
       </c>
       <c r="AM172" s="0" t="inlineStr">
         <is>
-          <t>热情洋溢！</t>
+          <t>龙之研习</t>
         </is>
       </c>
       <c r="AN172" s="0" t="inlineStr">
         <is>
-          <t>火爆飞踢</t>
+          <t>超级灼热龙息</t>
         </is>
       </c>
       <c r="AO172" s="0" t="inlineStr">
         <is>
-          <t>依依不舍</t>
+          <t>阿嚏！</t>
         </is>
       </c>
       <c r="AP172" s="0" t="inlineStr">
         <is>
-          <t>融融情谊</t>
+          <t>扑棱，扑棱，扑棱！</t>
         </is>
       </c>
       <c r="AQ172" s="0" t="inlineStr">
         <is>
-          <t>生生不息</t>
+          <t>妈----！</t>
         </is>
       </c>
     </row>
@@ -51202,21 +51050,21 @@
         <v>171</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>不落魔锋</t>
+          <t>明烛</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
-          <t>亚恒</t>
+          <t>米利欧</t>
         </is>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
-          <t>Zaahen</t>
+          <t>Milio</t>
         </is>
       </c>
       <c r="F173" s="0" t="inlineStr">
@@ -51224,52 +51072,64 @@
           <t>√</t>
         </is>
       </c>
-      <c r="G173" s="0" t="inlineStr"/>
-      <c r="H173" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I173" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J173" s="0" t="inlineStr"/>
+      <c r="G173" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="H173" s="0" t="inlineStr"/>
+      <c r="I173" s="0" t="inlineStr"/>
+      <c r="J173" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K173" s="0" t="inlineStr"/>
-      <c r="L173" s="0" t="inlineStr"/>
+      <c r="L173" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="M173" s="0" t="inlineStr"/>
-      <c r="N173" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O173" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N173" s="0" t="inlineStr"/>
+      <c r="O173" s="0" t="inlineStr"/>
       <c r="P173" s="0" t="inlineStr"/>
       <c r="Q173" s="0" t="inlineStr"/>
-      <c r="R173" s="0" t="inlineStr"/>
+      <c r="R173" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="S173" s="0" t="inlineStr">
         <is>
-          <t>物理伤害</t>
+          <t>魔法伤害</t>
         </is>
       </c>
       <c r="T173" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U173" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V173" s="0" t="inlineStr"/>
-      <c r="W173" s="0" t="inlineStr"/>
+      <c r="V173" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="W173" s="0" t="inlineStr">
+        <is>
+          <t>2024-07-06 23-54-41</t>
+        </is>
+      </c>
       <c r="X173" s="0" t="inlineStr"/>
       <c r="Y173" s="0" t="inlineStr"/>
       <c r="Z173" s="0" t="inlineStr"/>
       <c r="AA173" s="0" t="inlineStr"/>
-      <c r="AB173" s="0" t="inlineStr"/>
+      <c r="AB173" s="0" t="inlineStr">
+        <is>
+          <t>2024-07-06 23-54-41</t>
+        </is>
+      </c>
       <c r="AC173" s="0" t="inlineStr"/>
       <c r="AD173" s="0" t="n">
         <v>0</v>
@@ -51278,57 +51138,57 @@
       <c r="AF173" s="0" t="inlineStr"/>
       <c r="AG173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/904.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/902.png</t>
         </is>
       </c>
       <c r="AH173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Zaahen/Skins/Base/ZaahenLoadScreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Milio/Skins/Base/MilioLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Zaahen/Skins/Base/Images/Zaahen_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Milio/Skins/Base/Images/Milio_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/904.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/902.ogg</t>
         </is>
       </c>
       <c r="AK173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/904.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/902.ogg</t>
         </is>
       </c>
       <c r="AL173" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/904.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/902.ogg</t>
         </is>
       </c>
       <c r="AM173" s="0" t="inlineStr">
         <is>
-          <t>不落之志</t>
+          <t>热情洋溢！</t>
         </is>
       </c>
       <c r="AN173" s="0" t="inlineStr">
         <is>
-          <t>暗裔长刀</t>
+          <t>火爆飞踢</t>
         </is>
       </c>
       <c r="AO173" s="0" t="inlineStr">
         <is>
-          <t>厄影回锋</t>
+          <t>依依不舍</t>
         </is>
       </c>
       <c r="AP173" s="0" t="inlineStr">
         <is>
-          <t>赤金突袭</t>
+          <t>融融情谊</t>
         </is>
       </c>
       <c r="AQ173" s="0" t="inlineStr">
         <is>
-          <t>大赦</t>
+          <t>生生不息</t>
         </is>
       </c>
     </row>
@@ -51337,21 +51197,21 @@
         <v>172</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>异画师</t>
+          <t>不落魔锋</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>彗</t>
+          <t>亚恒</t>
         </is>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
-          <t>Hwei</t>
+          <t>Zaahen</t>
         </is>
       </c>
       <c r="F174" s="0" t="inlineStr">
@@ -51360,63 +51220,55 @@
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr"/>
-      <c r="H174" s="0" t="inlineStr"/>
-      <c r="I174" s="0" t="inlineStr"/>
-      <c r="J174" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="H174" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="I174" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="J174" s="0" t="inlineStr"/>
       <c r="K174" s="0" t="inlineStr"/>
-      <c r="L174" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="L174" s="0" t="inlineStr"/>
       <c r="M174" s="0" t="inlineStr"/>
-      <c r="N174" s="0" t="inlineStr"/>
-      <c r="O174" s="0" t="inlineStr"/>
-      <c r="P174" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="N174" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="O174" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="P174" s="0" t="inlineStr"/>
       <c r="Q174" s="0" t="inlineStr"/>
-      <c r="R174" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="R174" s="0" t="inlineStr"/>
       <c r="S174" s="0" t="inlineStr">
         <is>
-          <t>魔法伤害</t>
+          <t>物理伤害</t>
         </is>
       </c>
       <c r="T174" s="0" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U174" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V174" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="W174" s="0" t="inlineStr">
-        <is>
-          <t>2024-09-11 02-44-10</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V174" s="0" t="inlineStr"/>
+      <c r="W174" s="0" t="inlineStr"/>
       <c r="X174" s="0" t="inlineStr"/>
       <c r="Y174" s="0" t="inlineStr"/>
-      <c r="Z174" s="0" t="inlineStr"/>
+      <c r="Z174" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="AA174" s="0" t="inlineStr"/>
-      <c r="AB174" s="0" t="inlineStr">
-        <is>
-          <t>2024-09-11 02-44-10</t>
-        </is>
-      </c>
+      <c r="AB174" s="0" t="inlineStr"/>
       <c r="AC174" s="0" t="inlineStr"/>
       <c r="AD174" s="0" t="n">
         <v>0</v>
@@ -51425,57 +51277,57 @@
       <c r="AF174" s="0" t="inlineStr"/>
       <c r="AG174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/910.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/904.png</t>
         </is>
       </c>
       <c r="AH174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Hwei/Skins/Skin0/HweiLoadScreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Zaahen/Skins/Base/ZaahenLoadScreen_0.jpg</t>
         </is>
       </c>
       <c r="AI174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Hwei/Skins/Skin0/Images/hwei_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Zaahen/Skins/Base/Images/Zaahen_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/910.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/904.ogg</t>
         </is>
       </c>
       <c r="AK174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/910.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/904.ogg</t>
         </is>
       </c>
       <c r="AL174" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/910.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/904.ogg</t>
         </is>
       </c>
       <c r="AM174" s="0" t="inlineStr">
         <is>
-          <t>落款</t>
+          <t>不落之志</t>
         </is>
       </c>
       <c r="AN174" s="0" t="inlineStr">
         <is>
-          <t>主题：灾</t>
+          <t>暗裔长刀</t>
         </is>
       </c>
       <c r="AO174" s="0" t="inlineStr">
         <is>
-          <t>主题：靖</t>
+          <t>厄影回锋</t>
         </is>
       </c>
       <c r="AP174" s="0" t="inlineStr">
         <is>
-          <t>主题：悚</t>
+          <t>赤金突袭</t>
         </is>
       </c>
       <c r="AQ174" s="0" t="inlineStr">
         <is>
-          <t>焚心绚华绘</t>
+          <t>大赦</t>
         </is>
       </c>
     </row>
@@ -51484,21 +51336,21 @@
         <v>173</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>百裂冥犬</t>
+          <t>异画师</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
         <is>
-          <t>纳亚菲利</t>
+          <t>彗</t>
         </is>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
-          <t>Naafiri</t>
+          <t>Hwei</t>
         </is>
       </c>
       <c r="F175" s="0" t="inlineStr">
@@ -51507,43 +51359,47 @@
         </is>
       </c>
       <c r="G175" s="0" t="inlineStr"/>
-      <c r="H175" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I175" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J175" s="0" t="inlineStr"/>
+      <c r="H175" s="0" t="inlineStr"/>
+      <c r="I175" s="0" t="inlineStr"/>
+      <c r="J175" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K175" s="0" t="inlineStr"/>
-      <c r="L175" s="0" t="inlineStr"/>
+      <c r="L175" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="M175" s="0" t="inlineStr"/>
       <c r="N175" s="0" t="inlineStr"/>
-      <c r="O175" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="O175" s="0" t="inlineStr"/>
       <c r="P175" s="0" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="Q175" s="0" t="inlineStr"/>
-      <c r="R175" s="0" t="inlineStr"/>
+      <c r="Q175" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="R175" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="S175" s="0" t="inlineStr">
         <is>
-          <t>物理伤害</t>
+          <t>魔法伤害</t>
         </is>
       </c>
       <c r="T175" s="0" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U175" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V175" s="0" t="inlineStr">
         <is>
@@ -51572,57 +51428,57 @@
       <c r="AF175" s="0" t="inlineStr"/>
       <c r="AG175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/950.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/910.png</t>
         </is>
       </c>
       <c r="AH175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Naafiri/Skins/Base/NaafiriLoadscreen_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Hwei/Skins/Skin0/HweiLoadScreen_0.jpg</t>
         </is>
       </c>
       <c r="AI175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Naafiri/Skins/Base/Images/naafiri_splash_centered_0.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Hwei/Skins/Skin0/Images/hwei_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/950.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/910.ogg</t>
         </is>
       </c>
       <c r="AK175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/950.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/910.ogg</t>
         </is>
       </c>
       <c r="AL175" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/950.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/910.ogg</t>
         </is>
       </c>
       <c r="AM175" s="0" t="inlineStr">
         <is>
-          <t>狂烈种群</t>
+          <t>落款</t>
         </is>
       </c>
       <c r="AN175" s="0" t="inlineStr">
         <is>
-          <t>暗裔犬牙</t>
+          <t>主题：灾</t>
         </is>
       </c>
       <c r="AO175" s="0" t="inlineStr">
         <is>
-          <t>暴吼</t>
+          <t>主题：靖</t>
         </is>
       </c>
       <c r="AP175" s="0" t="inlineStr">
         <is>
-          <t>剔骨本能</t>
+          <t>主题：悚</t>
         </is>
       </c>
       <c r="AQ175" s="0" t="inlineStr">
         <is>
-          <t>猎狗血性</t>
+          <t>焚心绚华绘</t>
         </is>
       </c>
     </row>
@@ -51631,22 +51487,34 @@
         <v>174</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>66600</v>
+        <v>950</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>末日人机 厄加特</t>
-        </is>
-      </c>
-      <c r="D176" s="0" t="inlineStr"/>
+          <t>百裂冥犬</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>纳亚菲利</t>
+        </is>
+      </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
-          <t>Ruby_Urgot</t>
-        </is>
-      </c>
-      <c r="F176" s="0" t="inlineStr"/>
+          <t>Naafiri</t>
+        </is>
+      </c>
+      <c r="F176" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G176" s="0" t="inlineStr"/>
-      <c r="H176" s="0" t="inlineStr"/>
+      <c r="H176" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="I176" s="0" t="inlineStr">
         <is>
           <t>√</t>
@@ -51655,23 +51523,19 @@
       <c r="J176" s="0" t="inlineStr"/>
       <c r="K176" s="0" t="inlineStr"/>
       <c r="L176" s="0" t="inlineStr"/>
-      <c r="M176" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N176" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O176" s="0" t="inlineStr"/>
-      <c r="P176" s="0" t="inlineStr"/>
-      <c r="Q176" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
+      <c r="M176" s="0" t="inlineStr"/>
+      <c r="N176" s="0" t="inlineStr"/>
+      <c r="O176" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="P176" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="Q176" s="0" t="inlineStr"/>
       <c r="R176" s="0" t="inlineStr"/>
       <c r="S176" s="0" t="inlineStr">
         <is>
@@ -51679,18 +51543,30 @@
         </is>
       </c>
       <c r="T176" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U176" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V176" s="0" t="inlineStr"/>
-      <c r="W176" s="0" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V176" s="0" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="W176" s="0" t="inlineStr">
+        <is>
+          <t>2024-09-11 02-44-10</t>
+        </is>
+      </c>
       <c r="X176" s="0" t="inlineStr"/>
       <c r="Y176" s="0" t="inlineStr"/>
       <c r="Z176" s="0" t="inlineStr"/>
       <c r="AA176" s="0" t="inlineStr"/>
-      <c r="AB176" s="0" t="inlineStr"/>
+      <c r="AB176" s="0" t="inlineStr">
+        <is>
+          <t>2024-09-11 02-44-10</t>
+        </is>
+      </c>
       <c r="AC176" s="0" t="inlineStr"/>
       <c r="AD176" s="0" t="n">
         <v>0</v>
@@ -51699,2363 +51575,57 @@
       <c r="AF176" s="0" t="inlineStr"/>
       <c r="AG176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66600.png</t>
+          <t>/lol-game-data/assets/v1/champion-icons/950.png</t>
         </is>
       </c>
       <c r="AH176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Urgot/Skins/Base/UrgotLoadscreen_23.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Naafiri/Skins/Base/NaafiriLoadscreen_0.jpg</t>
         </is>
       </c>
       <c r="AI176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Urgot/Skins/Base/Images/urgot_splash_centered_23.jpg</t>
+          <t>/lol-game-data/assets/ASSETS/Characters/Naafiri/Skins/Base/Images/naafiri_splash_centered_0.jpg</t>
         </is>
       </c>
       <c r="AJ176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66600.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-sfx-audios/950.ogg</t>
         </is>
       </c>
       <c r="AK176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66600.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-choose-vo/950.ogg</t>
         </is>
       </c>
       <c r="AL176" s="0" t="inlineStr">
         <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66600.ogg</t>
+          <t>/lol-game-data/assets/v1/champion-ban-vo/950.ogg</t>
         </is>
       </c>
       <c r="AM176" s="0" t="inlineStr">
         <is>
-          <t>回响烈焰</t>
+          <t>狂烈种群</t>
         </is>
       </c>
       <c r="AN176" s="0" t="inlineStr">
         <is>
-          <t>腐蚀电荷</t>
+          <t>暗裔犬牙</t>
         </is>
       </c>
       <c r="AO176" s="0" t="inlineStr">
         <is>
-          <t>净除</t>
+          <t>暴吼</t>
         </is>
       </c>
       <c r="AP176" s="0" t="inlineStr">
         <is>
-          <t>鄙弃</t>
+          <t>剔骨本能</t>
         </is>
       </c>
       <c r="AQ176" s="0" t="inlineStr">
         <is>
-          <t>超越死亡的恐惧</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="B177" s="0" t="n">
-        <v>66602</v>
-      </c>
-      <c r="C177" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 库奇</t>
-        </is>
-      </c>
-      <c r="D177" s="0" t="inlineStr"/>
-      <c r="E177" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Corki</t>
-        </is>
-      </c>
-      <c r="F177" s="0" t="inlineStr"/>
-      <c r="G177" s="0" t="inlineStr"/>
-      <c r="H177" s="0" t="inlineStr"/>
-      <c r="I177" s="0" t="inlineStr"/>
-      <c r="J177" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K177" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="L177" s="0" t="inlineStr"/>
-      <c r="M177" s="0" t="inlineStr"/>
-      <c r="N177" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O177" s="0" t="inlineStr"/>
-      <c r="P177" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q177" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R177" s="0" t="inlineStr"/>
-      <c r="S177" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T177" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="U177" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V177" s="0" t="inlineStr"/>
-      <c r="W177" s="0" t="inlineStr"/>
-      <c r="X177" s="0" t="inlineStr"/>
-      <c r="Y177" s="0" t="inlineStr"/>
-      <c r="Z177" s="0" t="inlineStr"/>
-      <c r="AA177" s="0" t="inlineStr"/>
-      <c r="AB177" s="0" t="inlineStr"/>
-      <c r="AC177" s="0" t="inlineStr"/>
-      <c r="AD177" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE177" s="0" t="inlineStr"/>
-      <c r="AF177" s="0" t="inlineStr"/>
-      <c r="AG177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66602.png</t>
-        </is>
-      </c>
-      <c r="AH177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Corki/Skins/Base/CorkiLoadScreen_1.jpg</t>
-        </is>
-      </c>
-      <c r="AI177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Corki/Skins/Base/Images/corki_splash_centered_1.jpg</t>
-        </is>
-      </c>
-      <c r="AJ177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66602.ogg</t>
-        </is>
-      </c>
-      <c r="AK177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66602.ogg</t>
-        </is>
-      </c>
-      <c r="AL177" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66602.ogg</t>
-        </is>
-      </c>
-      <c r="AM177" s="0" t="inlineStr">
-        <is>
-          <t>海克斯科技军备</t>
-        </is>
-      </c>
-      <c r="AN177" s="0" t="inlineStr">
-        <is>
-          <t>磷光炸弹</t>
-        </is>
-      </c>
-      <c r="AO177" s="0" t="inlineStr">
-        <is>
-          <t>瓦尔基里俯冲</t>
-        </is>
-      </c>
-      <c r="AP177" s="0" t="inlineStr">
-        <is>
-          <t>格林机枪</t>
-        </is>
-      </c>
-      <c r="AQ177" s="0" t="inlineStr">
-        <is>
-          <t>火箭轰击</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="B178" s="0" t="n">
-        <v>66603</v>
-      </c>
-      <c r="C178" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 拉克丝</t>
-        </is>
-      </c>
-      <c r="D178" s="0" t="inlineStr"/>
-      <c r="E178" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Lux</t>
-        </is>
-      </c>
-      <c r="F178" s="0" t="inlineStr"/>
-      <c r="G178" s="0" t="inlineStr"/>
-      <c r="H178" s="0" t="inlineStr"/>
-      <c r="I178" s="0" t="inlineStr"/>
-      <c r="J178" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K178" s="0" t="inlineStr"/>
-      <c r="L178" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M178" s="0" t="inlineStr"/>
-      <c r="N178" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O178" s="0" t="inlineStr"/>
-      <c r="P178" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q178" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R178" s="0" t="inlineStr"/>
-      <c r="S178" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T178" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="U178" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V178" s="0" t="inlineStr"/>
-      <c r="W178" s="0" t="inlineStr"/>
-      <c r="X178" s="0" t="inlineStr"/>
-      <c r="Y178" s="0" t="inlineStr"/>
-      <c r="Z178" s="0" t="inlineStr"/>
-      <c r="AA178" s="0" t="inlineStr"/>
-      <c r="AB178" s="0" t="inlineStr"/>
-      <c r="AC178" s="0" t="inlineStr"/>
-      <c r="AD178" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE178" s="0" t="inlineStr"/>
-      <c r="AF178" s="0" t="inlineStr"/>
-      <c r="AG178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66603.png</t>
-        </is>
-      </c>
-      <c r="AH178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Lux/Skins/Base/LuxLoadscreen_17.jpg</t>
-        </is>
-      </c>
-      <c r="AI178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Lux/Skins/Base/Images/lux_splash_centered_17.jpg</t>
-        </is>
-      </c>
-      <c r="AJ178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66603.ogg</t>
-        </is>
-      </c>
-      <c r="AK178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66603.ogg</t>
-        </is>
-      </c>
-      <c r="AL178" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66603.ogg</t>
-        </is>
-      </c>
-      <c r="AM178" s="0" t="inlineStr">
-        <is>
-          <t>光芒四射</t>
-        </is>
-      </c>
-      <c r="AN178" s="0" t="inlineStr">
-        <is>
-          <t>光之束缚</t>
-        </is>
-      </c>
-      <c r="AO178" s="0" t="inlineStr">
-        <is>
-          <t>曲光屏障</t>
-        </is>
-      </c>
-      <c r="AP178" s="0" t="inlineStr">
-        <is>
-          <t>透光奇点</t>
-        </is>
-      </c>
-      <c r="AQ178" s="0" t="inlineStr">
-        <is>
-          <t>终极闪光</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="B179" s="0" t="n">
-        <v>66604</v>
-      </c>
-      <c r="C179" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 阿木木</t>
-        </is>
-      </c>
-      <c r="D179" s="0" t="inlineStr"/>
-      <c r="E179" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Amumu</t>
-        </is>
-      </c>
-      <c r="F179" s="0" t="inlineStr"/>
-      <c r="G179" s="0" t="inlineStr"/>
-      <c r="H179" s="0" t="inlineStr"/>
-      <c r="I179" s="0" t="inlineStr"/>
-      <c r="J179" s="0" t="inlineStr"/>
-      <c r="K179" s="0" t="inlineStr"/>
-      <c r="L179" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M179" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N179" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O179" s="0" t="inlineStr"/>
-      <c r="P179" s="0" t="inlineStr"/>
-      <c r="Q179" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R179" s="0" t="inlineStr"/>
-      <c r="S179" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T179" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="U179" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V179" s="0" t="inlineStr"/>
-      <c r="W179" s="0" t="inlineStr"/>
-      <c r="X179" s="0" t="inlineStr"/>
-      <c r="Y179" s="0" t="inlineStr"/>
-      <c r="Z179" s="0" t="inlineStr"/>
-      <c r="AA179" s="0" t="inlineStr"/>
-      <c r="AB179" s="0" t="inlineStr"/>
-      <c r="AC179" s="0" t="inlineStr"/>
-      <c r="AD179" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE179" s="0" t="inlineStr"/>
-      <c r="AF179" s="0" t="inlineStr"/>
-      <c r="AG179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66604.png</t>
-        </is>
-      </c>
-      <c r="AH179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Amumu/Skins/Base/AmumuLoadscreen_24.jpg</t>
-        </is>
-      </c>
-      <c r="AI179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Amumu/Skins/Base/Images/amumu_splash_centered_24.jpg</t>
-        </is>
-      </c>
-      <c r="AJ179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66604.ogg</t>
-        </is>
-      </c>
-      <c r="AK179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66604.ogg</t>
-        </is>
-      </c>
-      <c r="AL179" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66604.ogg</t>
-        </is>
-      </c>
-      <c r="AM179" s="0" t="inlineStr">
-        <is>
-          <t>诅咒之触</t>
-        </is>
-      </c>
-      <c r="AN179" s="0" t="inlineStr">
-        <is>
-          <t>绷带牵引</t>
-        </is>
-      </c>
-      <c r="AO179" s="0" t="inlineStr">
-        <is>
-          <t>绝望光环</t>
-        </is>
-      </c>
-      <c r="AP179" s="0" t="inlineStr">
-        <is>
-          <t>阿木木的愤怒</t>
-        </is>
-      </c>
-      <c r="AQ179" s="0" t="inlineStr">
-        <is>
-          <t>木乃伊之咒</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="B180" s="0" t="n">
-        <v>66605</v>
-      </c>
-      <c r="C180" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 科加斯</t>
-        </is>
-      </c>
-      <c r="D180" s="0" t="inlineStr"/>
-      <c r="E180" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Chogath</t>
-        </is>
-      </c>
-      <c r="F180" s="0" t="inlineStr"/>
-      <c r="G180" s="0" t="inlineStr"/>
-      <c r="H180" s="0" t="inlineStr"/>
-      <c r="I180" s="0" t="inlineStr"/>
-      <c r="J180" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K180" s="0" t="inlineStr"/>
-      <c r="L180" s="0" t="inlineStr"/>
-      <c r="M180" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N180" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O180" s="0" t="inlineStr"/>
-      <c r="P180" s="0" t="inlineStr"/>
-      <c r="Q180" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R180" s="0" t="inlineStr"/>
-      <c r="S180" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T180" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="U180" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V180" s="0" t="inlineStr"/>
-      <c r="W180" s="0" t="inlineStr"/>
-      <c r="X180" s="0" t="inlineStr"/>
-      <c r="Y180" s="0" t="inlineStr"/>
-      <c r="Z180" s="0" t="inlineStr"/>
-      <c r="AA180" s="0" t="inlineStr"/>
-      <c r="AB180" s="0" t="inlineStr"/>
-      <c r="AC180" s="0" t="inlineStr"/>
-      <c r="AD180" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE180" s="0" t="inlineStr"/>
-      <c r="AF180" s="0" t="inlineStr"/>
-      <c r="AG180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66605.png</t>
-        </is>
-      </c>
-      <c r="AH180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Chogath/skins/base/ChogathLoadscreen_7.jpg</t>
-        </is>
-      </c>
-      <c r="AI180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Chogath/skins/base/Images/chogath_splash_centered_7.jpg</t>
-        </is>
-      </c>
-      <c r="AJ180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66605.ogg</t>
-        </is>
-      </c>
-      <c r="AK180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66605.ogg</t>
-        </is>
-      </c>
-      <c r="AL180" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66605.ogg</t>
-        </is>
-      </c>
-      <c r="AM180" s="0" t="inlineStr">
-        <is>
-          <t>肉食者</t>
-        </is>
-      </c>
-      <c r="AN180" s="0" t="inlineStr">
-        <is>
-          <t>破裂</t>
-        </is>
-      </c>
-      <c r="AO180" s="0" t="inlineStr">
-        <is>
-          <t>野性尖叫</t>
-        </is>
-      </c>
-      <c r="AP180" s="0" t="inlineStr">
-        <is>
-          <t>恐惧之刺</t>
-        </is>
-      </c>
-      <c r="AQ180" s="0" t="inlineStr">
-        <is>
-          <t>盛宴</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="B181" s="0" t="n">
-        <v>66606</v>
-      </c>
-      <c r="C181" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 崔丝塔娜</t>
-        </is>
-      </c>
-      <c r="D181" s="0" t="inlineStr"/>
-      <c r="E181" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Tristana</t>
-        </is>
-      </c>
-      <c r="F181" s="0" t="inlineStr"/>
-      <c r="G181" s="0" t="inlineStr"/>
-      <c r="H181" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I181" s="0" t="inlineStr"/>
-      <c r="J181" s="0" t="inlineStr"/>
-      <c r="K181" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="L181" s="0" t="inlineStr"/>
-      <c r="M181" s="0" t="inlineStr"/>
-      <c r="N181" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O181" s="0" t="inlineStr"/>
-      <c r="P181" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q181" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R181" s="0" t="inlineStr"/>
-      <c r="S181" s="0" t="inlineStr">
-        <is>
-          <t>物理伤害</t>
-        </is>
-      </c>
-      <c r="T181" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="U181" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V181" s="0" t="inlineStr"/>
-      <c r="W181" s="0" t="inlineStr"/>
-      <c r="X181" s="0" t="inlineStr"/>
-      <c r="Y181" s="0" t="inlineStr"/>
-      <c r="Z181" s="0" t="inlineStr"/>
-      <c r="AA181" s="0" t="inlineStr"/>
-      <c r="AB181" s="0" t="inlineStr"/>
-      <c r="AC181" s="0" t="inlineStr"/>
-      <c r="AD181" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE181" s="0" t="inlineStr"/>
-      <c r="AF181" s="0" t="inlineStr"/>
-      <c r="AG181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66606.png</t>
-        </is>
-      </c>
-      <c r="AH181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Tristana/Skins/Base/TristanaLoadscreen_24.jpg</t>
-        </is>
-      </c>
-      <c r="AI181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Tristana/Skins/Base/Images/tristana_splash_centered_24.jpg</t>
-        </is>
-      </c>
-      <c r="AJ181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66606.ogg</t>
-        </is>
-      </c>
-      <c r="AK181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66606.ogg</t>
-        </is>
-      </c>
-      <c r="AL181" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66606.ogg</t>
-        </is>
-      </c>
-      <c r="AM181" s="0" t="inlineStr">
-        <is>
-          <t>瞄准</t>
-        </is>
-      </c>
-      <c r="AN181" s="0" t="inlineStr">
-        <is>
-          <t>急速射击</t>
-        </is>
-      </c>
-      <c r="AO181" s="0" t="inlineStr">
-        <is>
-          <t>火箭跳跃</t>
-        </is>
-      </c>
-      <c r="AP181" s="0" t="inlineStr">
-        <is>
-          <t>爆炸火花</t>
-        </is>
-      </c>
-      <c r="AQ181" s="0" t="inlineStr">
-        <is>
-          <t>毁灭射击</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="B182" s="0" t="n">
-        <v>66607</v>
-      </c>
-      <c r="C182" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 娜美</t>
-        </is>
-      </c>
-      <c r="D182" s="0" t="inlineStr"/>
-      <c r="E182" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Nami</t>
-        </is>
-      </c>
-      <c r="F182" s="0" t="inlineStr"/>
-      <c r="G182" s="0" t="inlineStr"/>
-      <c r="H182" s="0" t="inlineStr"/>
-      <c r="I182" s="0" t="inlineStr"/>
-      <c r="J182" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K182" s="0" t="inlineStr"/>
-      <c r="L182" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M182" s="0" t="inlineStr"/>
-      <c r="N182" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O182" s="0" t="inlineStr"/>
-      <c r="P182" s="0" t="inlineStr"/>
-      <c r="Q182" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R182" s="0" t="inlineStr"/>
-      <c r="S182" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T182" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="U182" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V182" s="0" t="inlineStr"/>
-      <c r="W182" s="0" t="inlineStr"/>
-      <c r="X182" s="0" t="inlineStr"/>
-      <c r="Y182" s="0" t="inlineStr"/>
-      <c r="Z182" s="0" t="inlineStr"/>
-      <c r="AA182" s="0" t="inlineStr"/>
-      <c r="AB182" s="0" t="inlineStr"/>
-      <c r="AC182" s="0" t="inlineStr"/>
-      <c r="AD182" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE182" s="0" t="inlineStr"/>
-      <c r="AF182" s="0" t="inlineStr"/>
-      <c r="AG182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66607.png</t>
-        </is>
-      </c>
-      <c r="AH182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Nami/Skins/Base/NamiLoadScreen_51.jpg</t>
-        </is>
-      </c>
-      <c r="AI182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Nami/Skins/Base/Images/nami_splash_centered_51.jpg</t>
-        </is>
-      </c>
-      <c r="AJ182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66607.ogg</t>
-        </is>
-      </c>
-      <c r="AK182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66607.ogg</t>
-        </is>
-      </c>
-      <c r="AL182" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66607.ogg</t>
-        </is>
-      </c>
-      <c r="AM182" s="0" t="inlineStr">
-        <is>
-          <t>踏浪之行</t>
-        </is>
-      </c>
-      <c r="AN182" s="0" t="inlineStr">
-        <is>
-          <t>碧波之牢</t>
-        </is>
-      </c>
-      <c r="AO182" s="0" t="inlineStr">
-        <is>
-          <t>冲击之潮</t>
-        </is>
-      </c>
-      <c r="AP182" s="0" t="inlineStr">
-        <is>
-          <t>唤潮之佑</t>
-        </is>
-      </c>
-      <c r="AQ182" s="0" t="inlineStr">
-        <is>
-          <t>怒涛之啸</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="B183" s="0" t="n">
-        <v>66608</v>
-      </c>
-      <c r="C183" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 李青</t>
-        </is>
-      </c>
-      <c r="D183" s="0" t="inlineStr"/>
-      <c r="E183" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_LeeSin</t>
-        </is>
-      </c>
-      <c r="F183" s="0" t="inlineStr"/>
-      <c r="G183" s="0" t="inlineStr"/>
-      <c r="H183" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I183" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J183" s="0" t="inlineStr"/>
-      <c r="K183" s="0" t="inlineStr"/>
-      <c r="L183" s="0" t="inlineStr"/>
-      <c r="M183" s="0" t="inlineStr"/>
-      <c r="N183" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O183" s="0" t="inlineStr"/>
-      <c r="P183" s="0" t="inlineStr"/>
-      <c r="Q183" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R183" s="0" t="inlineStr"/>
-      <c r="S183" s="0" t="inlineStr">
-        <is>
-          <t>物理伤害</t>
-        </is>
-      </c>
-      <c r="T183" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U183" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V183" s="0" t="inlineStr"/>
-      <c r="W183" s="0" t="inlineStr"/>
-      <c r="X183" s="0" t="inlineStr"/>
-      <c r="Y183" s="0" t="inlineStr"/>
-      <c r="Z183" s="0" t="inlineStr"/>
-      <c r="AA183" s="0" t="inlineStr"/>
-      <c r="AB183" s="0" t="inlineStr"/>
-      <c r="AC183" s="0" t="inlineStr"/>
-      <c r="AD183" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE183" s="0" t="inlineStr"/>
-      <c r="AF183" s="0" t="inlineStr"/>
-      <c r="AG183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66608.png</t>
-        </is>
-      </c>
-      <c r="AH183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_LeeSin/Skins/Skin27/Ruby_LeeSinLoadscreen_27.jpg</t>
-        </is>
-      </c>
-      <c r="AI183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_LeeSin/Skins/Skin27/Images/Ruby_LeeSin_splash_centered_27.jpg</t>
-        </is>
-      </c>
-      <c r="AJ183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66608.ogg</t>
-        </is>
-      </c>
-      <c r="AK183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66608.ogg</t>
-        </is>
-      </c>
-      <c r="AL183" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66608.ogg</t>
-        </is>
-      </c>
-      <c r="AM183" s="0" t="inlineStr">
-        <is>
-          <t>疾风骤雨</t>
-        </is>
-      </c>
-      <c r="AN183" s="0" t="inlineStr">
-        <is>
-          <t>天音波/回音击</t>
-        </is>
-      </c>
-      <c r="AO183" s="0" t="inlineStr">
-        <is>
-          <t>金钟罩/铁布衫</t>
-        </is>
-      </c>
-      <c r="AP183" s="0" t="inlineStr">
-        <is>
-          <t>天雷破/摧筋断骨</t>
-        </is>
-      </c>
-      <c r="AQ183" s="0" t="inlineStr">
-        <is>
-          <t>猛龙摆尾</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="B184" s="0" t="n">
-        <v>66609</v>
-      </c>
-      <c r="C184" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 凯特琳</t>
-        </is>
-      </c>
-      <c r="D184" s="0" t="inlineStr"/>
-      <c r="E184" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Caitlyn</t>
-        </is>
-      </c>
-      <c r="F184" s="0" t="inlineStr"/>
-      <c r="G184" s="0" t="inlineStr"/>
-      <c r="H184" s="0" t="inlineStr"/>
-      <c r="I184" s="0" t="inlineStr"/>
-      <c r="J184" s="0" t="inlineStr"/>
-      <c r="K184" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="L184" s="0" t="inlineStr"/>
-      <c r="M184" s="0" t="inlineStr"/>
-      <c r="N184" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O184" s="0" t="inlineStr"/>
-      <c r="P184" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q184" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R184" s="0" t="inlineStr"/>
-      <c r="S184" s="0" t="inlineStr">
-        <is>
-          <t>物理伤害</t>
-        </is>
-      </c>
-      <c r="T184" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="U184" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V184" s="0" t="inlineStr"/>
-      <c r="W184" s="0" t="inlineStr"/>
-      <c r="X184" s="0" t="inlineStr"/>
-      <c r="Y184" s="0" t="inlineStr"/>
-      <c r="Z184" s="0" t="inlineStr"/>
-      <c r="AA184" s="0" t="inlineStr"/>
-      <c r="AB184" s="0" t="inlineStr"/>
-      <c r="AC184" s="0" t="inlineStr"/>
-      <c r="AD184" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE184" s="0" t="inlineStr"/>
-      <c r="AF184" s="0" t="inlineStr"/>
-      <c r="AG184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66609.png</t>
-        </is>
-      </c>
-      <c r="AH184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Caitlyn/Skins/Skin06/Ruby_CaitlynLoadscreen_6.jpg</t>
-        </is>
-      </c>
-      <c r="AI184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Caitlyn/Skins/Skin06/Images/Ruby_Caitlyn_splash_centered_6.jpg</t>
-        </is>
-      </c>
-      <c r="AJ184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66609.ogg</t>
-        </is>
-      </c>
-      <c r="AK184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66609.ogg</t>
-        </is>
-      </c>
-      <c r="AL184" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66609.ogg</t>
-        </is>
-      </c>
-      <c r="AM184" s="0" t="inlineStr">
-        <is>
-          <t>爆头</t>
-        </is>
-      </c>
-      <c r="AN184" s="0" t="inlineStr">
-        <is>
-          <t>和平使者</t>
-        </is>
-      </c>
-      <c r="AO184" s="0" t="inlineStr">
-        <is>
-          <t>约德尔诱捕器</t>
-        </is>
-      </c>
-      <c r="AP184" s="0" t="inlineStr">
-        <is>
-          <t>90口径绳网</t>
-        </is>
-      </c>
-      <c r="AQ184" s="0" t="inlineStr">
-        <is>
-          <t>让子弹飞</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="B185" s="0" t="n">
-        <v>66610</v>
-      </c>
-      <c r="C185" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 诺提勒斯</t>
-        </is>
-      </c>
-      <c r="D185" s="0" t="inlineStr"/>
-      <c r="E185" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Nautilus</t>
-        </is>
-      </c>
-      <c r="F185" s="0" t="inlineStr"/>
-      <c r="G185" s="0" t="inlineStr"/>
-      <c r="H185" s="0" t="inlineStr"/>
-      <c r="I185" s="0" t="inlineStr"/>
-      <c r="J185" s="0" t="inlineStr"/>
-      <c r="K185" s="0" t="inlineStr"/>
-      <c r="L185" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M185" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N185" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O185" s="0" t="inlineStr"/>
-      <c r="P185" s="0" t="inlineStr"/>
-      <c r="Q185" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R185" s="0" t="inlineStr"/>
-      <c r="S185" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T185" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="U185" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V185" s="0" t="inlineStr"/>
-      <c r="W185" s="0" t="inlineStr"/>
-      <c r="X185" s="0" t="inlineStr"/>
-      <c r="Y185" s="0" t="inlineStr"/>
-      <c r="Z185" s="0" t="inlineStr"/>
-      <c r="AA185" s="0" t="inlineStr"/>
-      <c r="AB185" s="0" t="inlineStr"/>
-      <c r="AC185" s="0" t="inlineStr"/>
-      <c r="AD185" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE185" s="0" t="inlineStr"/>
-      <c r="AF185" s="0" t="inlineStr"/>
-      <c r="AG185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66610.png</t>
-        </is>
-      </c>
-      <c r="AH185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Nautilus/Skins/Skin18/Ruby_NautilusLoadscreen_18.jpg</t>
-        </is>
-      </c>
-      <c r="AI185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Nautilus/Skins/Base/Images/nautilus_splash_centered_18.jpg</t>
-        </is>
-      </c>
-      <c r="AJ185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66610.ogg</t>
-        </is>
-      </c>
-      <c r="AK185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66610.ogg</t>
-        </is>
-      </c>
-      <c r="AL185" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66610.ogg</t>
-        </is>
-      </c>
-      <c r="AM185" s="0" t="inlineStr">
-        <is>
-          <t>排山倒海</t>
-        </is>
-      </c>
-      <c r="AN185" s="0" t="inlineStr">
-        <is>
-          <t>疏通航道</t>
-        </is>
-      </c>
-      <c r="AO185" s="0" t="inlineStr">
-        <is>
-          <t>泰坦之怒</t>
-        </is>
-      </c>
-      <c r="AP185" s="0" t="inlineStr">
-        <is>
-          <t>暗流涌动</t>
-        </is>
-      </c>
-      <c r="AQ185" s="0" t="inlineStr">
-        <is>
-          <t>深海冲击</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="B186" s="0" t="n">
-        <v>66611</v>
-      </c>
-      <c r="C186" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 茂凯</t>
-        </is>
-      </c>
-      <c r="D186" s="0" t="inlineStr"/>
-      <c r="E186" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Maokai</t>
-        </is>
-      </c>
-      <c r="F186" s="0" t="inlineStr"/>
-      <c r="G186" s="0" t="inlineStr"/>
-      <c r="H186" s="0" t="inlineStr"/>
-      <c r="I186" s="0" t="inlineStr"/>
-      <c r="J186" s="0" t="inlineStr"/>
-      <c r="K186" s="0" t="inlineStr"/>
-      <c r="L186" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M186" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N186" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O186" s="0" t="inlineStr"/>
-      <c r="P186" s="0" t="inlineStr"/>
-      <c r="Q186" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R186" s="0" t="inlineStr"/>
-      <c r="S186" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T186" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="U186" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V186" s="0" t="inlineStr"/>
-      <c r="W186" s="0" t="inlineStr"/>
-      <c r="X186" s="0" t="inlineStr"/>
-      <c r="Y186" s="0" t="inlineStr"/>
-      <c r="Z186" s="0" t="inlineStr"/>
-      <c r="AA186" s="0" t="inlineStr"/>
-      <c r="AB186" s="0" t="inlineStr"/>
-      <c r="AC186" s="0" t="inlineStr"/>
-      <c r="AD186" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE186" s="0" t="inlineStr"/>
-      <c r="AF186" s="0" t="inlineStr"/>
-      <c r="AG186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66611.png</t>
-        </is>
-      </c>
-      <c r="AH186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Maokai/Skins/Skin04/Ruby_MaokaiLoadScreen_4.jpg</t>
-        </is>
-      </c>
-      <c r="AI186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Maokai/Skins/Skin04/Images/Ruby_Maokai_splash_centered_4.jpg</t>
-        </is>
-      </c>
-      <c r="AJ186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66611.ogg</t>
-        </is>
-      </c>
-      <c r="AK186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66611.ogg</t>
-        </is>
-      </c>
-      <c r="AL186" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66611.ogg</t>
-        </is>
-      </c>
-      <c r="AM186" s="0" t="inlineStr">
-        <is>
-          <t>吸元秘术</t>
-        </is>
-      </c>
-      <c r="AN186" s="0" t="inlineStr">
-        <is>
-          <t>荆棘重击</t>
-        </is>
-      </c>
-      <c r="AO186" s="0" t="inlineStr">
-        <is>
-          <t>扭曲突刺</t>
-        </is>
-      </c>
-      <c r="AP186" s="0" t="inlineStr">
-        <is>
-          <t>树苗投掷</t>
-        </is>
-      </c>
-      <c r="AQ186" s="0" t="inlineStr">
-        <is>
-          <t>自然之握</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="B187" s="0" t="n">
-        <v>66612</v>
-      </c>
-      <c r="C187" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 泽拉斯</t>
-        </is>
-      </c>
-      <c r="D187" s="0" t="inlineStr"/>
-      <c r="E187" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Xerath</t>
-        </is>
-      </c>
-      <c r="F187" s="0" t="inlineStr"/>
-      <c r="G187" s="0" t="inlineStr"/>
-      <c r="H187" s="0" t="inlineStr"/>
-      <c r="I187" s="0" t="inlineStr"/>
-      <c r="J187" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K187" s="0" t="inlineStr"/>
-      <c r="L187" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M187" s="0" t="inlineStr"/>
-      <c r="N187" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O187" s="0" t="inlineStr"/>
-      <c r="P187" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q187" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R187" s="0" t="inlineStr"/>
-      <c r="S187" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T187" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="U187" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V187" s="0" t="inlineStr"/>
-      <c r="W187" s="0" t="inlineStr"/>
-      <c r="X187" s="0" t="inlineStr"/>
-      <c r="Y187" s="0" t="inlineStr"/>
-      <c r="Z187" s="0" t="inlineStr"/>
-      <c r="AA187" s="0" t="inlineStr"/>
-      <c r="AB187" s="0" t="inlineStr"/>
-      <c r="AC187" s="0" t="inlineStr"/>
-      <c r="AD187" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE187" s="0" t="inlineStr"/>
-      <c r="AF187" s="0" t="inlineStr"/>
-      <c r="AG187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66612.png</t>
-        </is>
-      </c>
-      <c r="AH187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Xerath/Skins/Skin05/Ruby_XerathLoadscreen_5.jpg</t>
-        </is>
-      </c>
-      <c r="AI187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Xerath/Skins/Skin05/Images/Ruby_Xerath_splash_centered_5.jpg</t>
-        </is>
-      </c>
-      <c r="AJ187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66612.ogg</t>
-        </is>
-      </c>
-      <c r="AK187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66612.ogg</t>
-        </is>
-      </c>
-      <c r="AL187" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66612.ogg</t>
-        </is>
-      </c>
-      <c r="AM187" s="0" t="inlineStr">
-        <is>
-          <t>法力澎湃</t>
-        </is>
-      </c>
-      <c r="AN187" s="0" t="inlineStr">
-        <is>
-          <t>奥能脉冲</t>
-        </is>
-      </c>
-      <c r="AO187" s="0" t="inlineStr">
-        <is>
-          <t>毁灭之眼</t>
-        </is>
-      </c>
-      <c r="AP187" s="0" t="inlineStr">
-        <is>
-          <t>冲击法球</t>
-        </is>
-      </c>
-      <c r="AQ187" s="0" t="inlineStr">
-        <is>
-          <t>奥术仪式</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="B188" s="0" t="n">
-        <v>66613</v>
-      </c>
-      <c r="C188" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 布兰德</t>
-        </is>
-      </c>
-      <c r="D188" s="0" t="inlineStr"/>
-      <c r="E188" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Brand</t>
-        </is>
-      </c>
-      <c r="F188" s="0" t="inlineStr"/>
-      <c r="G188" s="0" t="inlineStr"/>
-      <c r="H188" s="0" t="inlineStr"/>
-      <c r="I188" s="0" t="inlineStr"/>
-      <c r="J188" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K188" s="0" t="inlineStr"/>
-      <c r="L188" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M188" s="0" t="inlineStr"/>
-      <c r="N188" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O188" s="0" t="inlineStr"/>
-      <c r="P188" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q188" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R188" s="0" t="inlineStr"/>
-      <c r="S188" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T188" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="U188" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V188" s="0" t="inlineStr"/>
-      <c r="W188" s="0" t="inlineStr"/>
-      <c r="X188" s="0" t="inlineStr"/>
-      <c r="Y188" s="0" t="inlineStr"/>
-      <c r="Z188" s="0" t="inlineStr"/>
-      <c r="AA188" s="0" t="inlineStr"/>
-      <c r="AB188" s="0" t="inlineStr"/>
-      <c r="AC188" s="0" t="inlineStr"/>
-      <c r="AD188" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE188" s="0" t="inlineStr"/>
-      <c r="AF188" s="0" t="inlineStr"/>
-      <c r="AG188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66613.png</t>
-        </is>
-      </c>
-      <c r="AH188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Brand/Skins/Skin04/Ruby_BrandLoadScreen_4.jpg</t>
-        </is>
-      </c>
-      <c r="AI188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Brand/Skins/Skin04/Images/Ruby_Brand_splash_centered_4.jpg</t>
-        </is>
-      </c>
-      <c r="AJ188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66613.ogg</t>
-        </is>
-      </c>
-      <c r="AK188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66613.ogg</t>
-        </is>
-      </c>
-      <c r="AL188" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66613.ogg</t>
-        </is>
-      </c>
-      <c r="AM188" s="0" t="inlineStr">
-        <is>
-          <t>炽热之焰</t>
-        </is>
-      </c>
-      <c r="AN188" s="0" t="inlineStr">
-        <is>
-          <t>火焰烙印</t>
-        </is>
-      </c>
-      <c r="AO188" s="0" t="inlineStr">
-        <is>
-          <t>烈焰之柱</t>
-        </is>
-      </c>
-      <c r="AP188" s="0" t="inlineStr">
-        <is>
-          <t>烈火燃烧</t>
-        </is>
-      </c>
-      <c r="AQ188" s="0" t="inlineStr">
-        <is>
-          <t>烈焰风暴</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="B189" s="0" t="n">
-        <v>66614</v>
-      </c>
-      <c r="C189" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 孙悟空</t>
-        </is>
-      </c>
-      <c r="D189" s="0" t="inlineStr"/>
-      <c r="E189" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Wukong</t>
-        </is>
-      </c>
-      <c r="F189" s="0" t="inlineStr"/>
-      <c r="G189" s="0" t="inlineStr"/>
-      <c r="H189" s="0" t="inlineStr"/>
-      <c r="I189" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J189" s="0" t="inlineStr"/>
-      <c r="K189" s="0" t="inlineStr"/>
-      <c r="L189" s="0" t="inlineStr"/>
-      <c r="M189" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N189" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O189" s="0" t="inlineStr"/>
-      <c r="P189" s="0" t="inlineStr"/>
-      <c r="Q189" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R189" s="0" t="inlineStr"/>
-      <c r="S189" s="0" t="inlineStr">
-        <is>
-          <t>物理伤害</t>
-        </is>
-      </c>
-      <c r="T189" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U189" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V189" s="0" t="inlineStr"/>
-      <c r="W189" s="0" t="inlineStr"/>
-      <c r="X189" s="0" t="inlineStr"/>
-      <c r="Y189" s="0" t="inlineStr"/>
-      <c r="Z189" s="0" t="inlineStr"/>
-      <c r="AA189" s="0" t="inlineStr"/>
-      <c r="AB189" s="0" t="inlineStr"/>
-      <c r="AC189" s="0" t="inlineStr"/>
-      <c r="AD189" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE189" s="0" t="inlineStr"/>
-      <c r="AF189" s="0" t="inlineStr"/>
-      <c r="AG189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66614.png</t>
-        </is>
-      </c>
-      <c r="AH189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Wukong/Skins/Skin04/Ruby_WukongLoadScreen_4.jpg</t>
-        </is>
-      </c>
-      <c r="AI189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Wukong/Skins/Skin04/Images/Ruby_Wukong_splash_centered_4.jpg</t>
-        </is>
-      </c>
-      <c r="AJ189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66614.ogg</t>
-        </is>
-      </c>
-      <c r="AK189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66614.ogg</t>
-        </is>
-      </c>
-      <c r="AL189" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66614.ogg</t>
-        </is>
-      </c>
-      <c r="AM189" s="0" t="inlineStr">
-        <is>
-          <t>金刚不坏</t>
-        </is>
-      </c>
-      <c r="AN189" s="0" t="inlineStr">
-        <is>
-          <t>粉碎打击</t>
-        </is>
-      </c>
-      <c r="AO189" s="0" t="inlineStr">
-        <is>
-          <t>真假猴王</t>
-        </is>
-      </c>
-      <c r="AP189" s="0" t="inlineStr">
-        <is>
-          <t>腾云突击</t>
-        </is>
-      </c>
-      <c r="AQ189" s="0" t="inlineStr">
-        <is>
-          <t>大闹天宫</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="B190" s="0" t="n">
-        <v>66615</v>
-      </c>
-      <c r="C190" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 索拉卡</t>
-        </is>
-      </c>
-      <c r="D190" s="0" t="inlineStr"/>
-      <c r="E190" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Soraka</t>
-        </is>
-      </c>
-      <c r="F190" s="0" t="inlineStr"/>
-      <c r="G190" s="0" t="inlineStr"/>
-      <c r="H190" s="0" t="inlineStr"/>
-      <c r="I190" s="0" t="inlineStr"/>
-      <c r="J190" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K190" s="0" t="inlineStr"/>
-      <c r="L190" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M190" s="0" t="inlineStr"/>
-      <c r="N190" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O190" s="0" t="inlineStr"/>
-      <c r="P190" s="0" t="inlineStr"/>
-      <c r="Q190" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R190" s="0" t="inlineStr"/>
-      <c r="S190" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T190" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="U190" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V190" s="0" t="inlineStr"/>
-      <c r="W190" s="0" t="inlineStr"/>
-      <c r="X190" s="0" t="inlineStr"/>
-      <c r="Y190" s="0" t="inlineStr"/>
-      <c r="Z190" s="0" t="inlineStr"/>
-      <c r="AA190" s="0" t="inlineStr"/>
-      <c r="AB190" s="0" t="inlineStr"/>
-      <c r="AC190" s="0" t="inlineStr"/>
-      <c r="AD190" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE190" s="0" t="inlineStr"/>
-      <c r="AF190" s="0" t="inlineStr"/>
-      <c r="AG190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66615.png</t>
-        </is>
-      </c>
-      <c r="AH190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Soraka/Skins/Skin04/Ruby_SorakaLoadScreen_4.jpg</t>
-        </is>
-      </c>
-      <c r="AI190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Soraka/Skins/Skin04/Images/Ruby_Soraka_splash_centered_4.jpg</t>
-        </is>
-      </c>
-      <c r="AJ190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66615.ogg</t>
-        </is>
-      </c>
-      <c r="AK190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66615.ogg</t>
-        </is>
-      </c>
-      <c r="AL190" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66615.ogg</t>
-        </is>
-      </c>
-      <c r="AM190" s="0" t="inlineStr">
-        <is>
-          <t>拯救</t>
-        </is>
-      </c>
-      <c r="AN190" s="0" t="inlineStr">
-        <is>
-          <t>流星坠落</t>
-        </is>
-      </c>
-      <c r="AO190" s="0" t="inlineStr">
-        <is>
-          <t>星之灌注</t>
-        </is>
-      </c>
-      <c r="AP190" s="0" t="inlineStr">
-        <is>
-          <t>星体结界</t>
-        </is>
-      </c>
-      <c r="AQ190" s="0" t="inlineStr">
-        <is>
-          <t>祈愿</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B191" s="0" t="n">
-        <v>66616</v>
-      </c>
-      <c r="C191" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 黛安娜</t>
-        </is>
-      </c>
-      <c r="D191" s="0" t="inlineStr"/>
-      <c r="E191" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Diana</t>
-        </is>
-      </c>
-      <c r="F191" s="0" t="inlineStr"/>
-      <c r="G191" s="0" t="inlineStr"/>
-      <c r="H191" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I191" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J191" s="0" t="inlineStr"/>
-      <c r="K191" s="0" t="inlineStr"/>
-      <c r="L191" s="0" t="inlineStr"/>
-      <c r="M191" s="0" t="inlineStr"/>
-      <c r="N191" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O191" s="0" t="inlineStr"/>
-      <c r="P191" s="0" t="inlineStr"/>
-      <c r="Q191" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R191" s="0" t="inlineStr"/>
-      <c r="S191" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T191" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="U191" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V191" s="0" t="inlineStr"/>
-      <c r="W191" s="0" t="inlineStr"/>
-      <c r="X191" s="0" t="inlineStr"/>
-      <c r="Y191" s="0" t="inlineStr"/>
-      <c r="Z191" s="0" t="inlineStr"/>
-      <c r="AA191" s="0" t="inlineStr"/>
-      <c r="AB191" s="0" t="inlineStr"/>
-      <c r="AC191" s="0" t="inlineStr"/>
-      <c r="AD191" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE191" s="0" t="inlineStr"/>
-      <c r="AF191" s="0" t="inlineStr"/>
-      <c r="AG191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66616.png</t>
-        </is>
-      </c>
-      <c r="AH191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Diana/Skins/skin03/Ruby_DianaLoadScreen_3.jpg</t>
-        </is>
-      </c>
-      <c r="AI191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Diana/Skins/skin03/Images/Ruby_Diana_splash_centered_3.jpg</t>
-        </is>
-      </c>
-      <c r="AJ191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66616.ogg</t>
-        </is>
-      </c>
-      <c r="AK191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66616.ogg</t>
-        </is>
-      </c>
-      <c r="AL191" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66616.ogg</t>
-        </is>
-      </c>
-      <c r="AM191" s="0" t="inlineStr">
-        <is>
-          <t>月银之刃</t>
-        </is>
-      </c>
-      <c r="AN191" s="0" t="inlineStr">
-        <is>
-          <t>新月打击</t>
-        </is>
-      </c>
-      <c r="AO191" s="0" t="inlineStr">
-        <is>
-          <t>苍白之瀑</t>
-        </is>
-      </c>
-      <c r="AP191" s="0" t="inlineStr">
-        <is>
-          <t>月神冲刺</t>
-        </is>
-      </c>
-      <c r="AQ191" s="0" t="inlineStr">
-        <is>
-          <t>月之降临</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="B192" s="0" t="n">
-        <v>66617</v>
-      </c>
-      <c r="C192" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 金克丝</t>
-        </is>
-      </c>
-      <c r="D192" s="0" t="inlineStr"/>
-      <c r="E192" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Jinx</t>
-        </is>
-      </c>
-      <c r="F192" s="0" t="inlineStr"/>
-      <c r="G192" s="0" t="inlineStr"/>
-      <c r="H192" s="0" t="inlineStr"/>
-      <c r="I192" s="0" t="inlineStr"/>
-      <c r="J192" s="0" t="inlineStr"/>
-      <c r="K192" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="L192" s="0" t="inlineStr"/>
-      <c r="M192" s="0" t="inlineStr"/>
-      <c r="N192" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O192" s="0" t="inlineStr"/>
-      <c r="P192" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q192" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R192" s="0" t="inlineStr"/>
-      <c r="S192" s="0" t="inlineStr">
-        <is>
-          <t>物理伤害</t>
-        </is>
-      </c>
-      <c r="T192" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="U192" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V192" s="0" t="inlineStr"/>
-      <c r="W192" s="0" t="inlineStr"/>
-      <c r="X192" s="0" t="inlineStr"/>
-      <c r="Y192" s="0" t="inlineStr"/>
-      <c r="Z192" s="0" t="inlineStr"/>
-      <c r="AA192" s="0" t="inlineStr"/>
-      <c r="AB192" s="0" t="inlineStr"/>
-      <c r="AC192" s="0" t="inlineStr"/>
-      <c r="AD192" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE192" s="0" t="inlineStr"/>
-      <c r="AF192" s="0" t="inlineStr"/>
-      <c r="AG192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66617.png</t>
-        </is>
-      </c>
-      <c r="AH192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Jinx/Skins/Skin03/Ruby_JinxLoadScreen_3.jpg</t>
-        </is>
-      </c>
-      <c r="AI192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Jinx/Skins/Skin03/Images/Ruby_Jinx_splash_centered_3.jpg</t>
-        </is>
-      </c>
-      <c r="AJ192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66617.ogg</t>
-        </is>
-      </c>
-      <c r="AK192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66617.ogg</t>
-        </is>
-      </c>
-      <c r="AL192" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66617.ogg</t>
-        </is>
-      </c>
-      <c r="AM192" s="0" t="inlineStr">
-        <is>
-          <t>罪恶快感</t>
-        </is>
-      </c>
-      <c r="AN192" s="0" t="inlineStr">
-        <is>
-          <t>枪炮交响曲！</t>
-        </is>
-      </c>
-      <c r="AO192" s="0" t="inlineStr">
-        <is>
-          <t>震荡电磁波！</t>
-        </is>
-      </c>
-      <c r="AP192" s="0" t="inlineStr">
-        <is>
-          <t>嚼火者手雷！</t>
-        </is>
-      </c>
-      <c r="AQ192" s="0" t="inlineStr">
-        <is>
-          <t>超究极死神飞弹！</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="B193" s="0" t="n">
-        <v>66618</v>
-      </c>
-      <c r="C193" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 玛尔扎哈</t>
-        </is>
-      </c>
-      <c r="D193" s="0" t="inlineStr"/>
-      <c r="E193" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Malzahar</t>
-        </is>
-      </c>
-      <c r="F193" s="0" t="inlineStr"/>
-      <c r="G193" s="0" t="inlineStr"/>
-      <c r="H193" s="0" t="inlineStr"/>
-      <c r="I193" s="0" t="inlineStr"/>
-      <c r="J193" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K193" s="0" t="inlineStr"/>
-      <c r="L193" s="0" t="inlineStr"/>
-      <c r="M193" s="0" t="inlineStr"/>
-      <c r="N193" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O193" s="0" t="inlineStr"/>
-      <c r="P193" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="Q193" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R193" s="0" t="inlineStr"/>
-      <c r="S193" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T193" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="U193" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V193" s="0" t="inlineStr"/>
-      <c r="W193" s="0" t="inlineStr"/>
-      <c r="X193" s="0" t="inlineStr"/>
-      <c r="Y193" s="0" t="inlineStr"/>
-      <c r="Z193" s="0" t="inlineStr"/>
-      <c r="AA193" s="0" t="inlineStr"/>
-      <c r="AB193" s="0" t="inlineStr"/>
-      <c r="AC193" s="0" t="inlineStr"/>
-      <c r="AD193" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE193" s="0" t="inlineStr"/>
-      <c r="AF193" s="0" t="inlineStr"/>
-      <c r="AG193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66618.png</t>
-        </is>
-      </c>
-      <c r="AH193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Malzahar/Skins/Base/Ruby_MalzaharLoadscreen.jpg</t>
-        </is>
-      </c>
-      <c r="AI193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Malzahar/Skins/Base/Images/Ruby_Malzahar_splash_centered_0.jpg</t>
-        </is>
-      </c>
-      <c r="AJ193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66618.ogg</t>
-        </is>
-      </c>
-      <c r="AK193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66618.ogg</t>
-        </is>
-      </c>
-      <c r="AL193" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66618.ogg</t>
-        </is>
-      </c>
-      <c r="AM193" s="0" t="inlineStr">
-        <is>
-          <t>虚空穿越</t>
-        </is>
-      </c>
-      <c r="AN193" s="0" t="inlineStr">
-        <is>
-          <t>虚空召唤</t>
-        </is>
-      </c>
-      <c r="AO193" s="0" t="inlineStr">
-        <is>
-          <t>虚空虫群</t>
-        </is>
-      </c>
-      <c r="AP193" s="0" t="inlineStr">
-        <is>
-          <t>煞星幻象</t>
-        </is>
-      </c>
-      <c r="AQ193" s="0" t="inlineStr">
-        <is>
-          <t>冥府之握</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B194" s="0" t="n">
-        <v>66619</v>
-      </c>
-      <c r="C194" s="0" t="inlineStr">
-        <is>
-          <t>末日人机 布里茨</t>
-        </is>
-      </c>
-      <c r="D194" s="0" t="inlineStr"/>
-      <c r="E194" s="0" t="inlineStr">
-        <is>
-          <t>Ruby_Blitzcrank</t>
-        </is>
-      </c>
-      <c r="F194" s="0" t="inlineStr"/>
-      <c r="G194" s="0" t="inlineStr"/>
-      <c r="H194" s="0" t="inlineStr"/>
-      <c r="I194" s="0" t="inlineStr"/>
-      <c r="J194" s="0" t="inlineStr"/>
-      <c r="K194" s="0" t="inlineStr"/>
-      <c r="L194" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="M194" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N194" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="O194" s="0" t="inlineStr"/>
-      <c r="P194" s="0" t="inlineStr"/>
-      <c r="Q194" s="0" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="R194" s="0" t="inlineStr"/>
-      <c r="S194" s="0" t="inlineStr">
-        <is>
-          <t>魔法伤害</t>
-        </is>
-      </c>
-      <c r="T194" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="U194" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V194" s="0" t="inlineStr"/>
-      <c r="W194" s="0" t="inlineStr"/>
-      <c r="X194" s="0" t="inlineStr"/>
-      <c r="Y194" s="0" t="inlineStr"/>
-      <c r="Z194" s="0" t="inlineStr"/>
-      <c r="AA194" s="0" t="inlineStr"/>
-      <c r="AB194" s="0" t="inlineStr"/>
-      <c r="AC194" s="0" t="inlineStr"/>
-      <c r="AD194" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE194" s="0" t="inlineStr"/>
-      <c r="AF194" s="0" t="inlineStr"/>
-      <c r="AG194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-icons/66619.png</t>
-        </is>
-      </c>
-      <c r="AH194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Blitzcrank/Skins/Skin22/Ruby_BlitzcrankLoadscreen_22.jpg</t>
-        </is>
-      </c>
-      <c r="AI194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/ASSETS/Characters/Ruby_Blitzcrank/Skins/Skin22/Images/Ruby_Blitzcrank_splash_centered_22.jpg</t>
-        </is>
-      </c>
-      <c r="AJ194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-sfx-audios/66619.ogg</t>
-        </is>
-      </c>
-      <c r="AK194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-choose-vo/66619.ogg</t>
-        </is>
-      </c>
-      <c r="AL194" s="0" t="inlineStr">
-        <is>
-          <t>/lol-game-data/assets/v1/champion-ban-vo/66619.ogg</t>
-        </is>
-      </c>
-      <c r="AM194" s="0" t="inlineStr">
-        <is>
-          <t>法力屏障</t>
-        </is>
-      </c>
-      <c r="AN194" s="0" t="inlineStr">
-        <is>
-          <t>机械飞爪</t>
-        </is>
-      </c>
-      <c r="AO194" s="0" t="inlineStr">
-        <is>
-          <t>过载运转</t>
-        </is>
-      </c>
-      <c r="AP194" s="0" t="inlineStr">
-        <is>
-          <t>能量铁拳</t>
-        </is>
-      </c>
-      <c r="AQ194" s="0" t="inlineStr">
-        <is>
-          <t>静电力场</t>
+          <t>猎狗血性</t>
         </is>
       </c>
     </row>
